--- a/Catapult Match report_UPL.xlsx
+++ b/Catapult Match report_UPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e184d086cb18a9d7/Desktop/FUFA/Match_Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{F5304803-8618-42B3-8165-1F34E63E08A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC0251A7-0776-41E0-A507-41E7F8B436F0}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{F5304803-8618-42B3-8165-1F34E63E08A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A9AB4A-A8DE-4099-9A7C-0EA2154DA48A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{F6077C19-DE50-4D6C-8F85-250EF59DDDF4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{F6077C19-DE50-4D6C-8F85-250EF59DDDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="182">
   <si>
     <t>Match Day</t>
   </si>
@@ -351,54 +351,6 @@
     <t>avg_total_decelerations</t>
   </si>
   <si>
-    <t>Sc Villa</t>
-  </si>
-  <si>
-    <t>Soltilo Bright Stars Fc</t>
-  </si>
-  <si>
-    <t>Kcca Fc</t>
-  </si>
-  <si>
-    <t>Maroons Fc</t>
-  </si>
-  <si>
-    <t>Bul Fc</t>
-  </si>
-  <si>
-    <t>Vipers Sc</t>
-  </si>
-  <si>
-    <t>Express Fc</t>
-  </si>
-  <si>
-    <t>Police Fc</t>
-  </si>
-  <si>
-    <t>Ura Fc</t>
-  </si>
-  <si>
-    <t>Wakiso Giants Fc</t>
-  </si>
-  <si>
-    <t>Mbarara City Fc</t>
-  </si>
-  <si>
-    <t>Lugazi Fc</t>
-  </si>
-  <si>
-    <t>Kitara Fc</t>
-  </si>
-  <si>
-    <t>Mbale Heroes Fc</t>
-  </si>
-  <si>
-    <t>Updf Fc</t>
-  </si>
-  <si>
-    <t>Nec Fc</t>
-  </si>
-  <si>
     <t>club_for</t>
   </si>
   <si>
@@ -429,9 +381,6 @@
     <t>avg_player_load</t>
   </si>
   <si>
-    <t>avg_power_score_wkg</t>
-  </si>
-  <si>
     <t>avg_work_ratio</t>
   </si>
   <si>
@@ -447,30 +396,6 @@
     <t>Average Deceleration Ccounts Per Min</t>
   </si>
   <si>
-    <t>max</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>std</t>
-  </si>
-  <si>
-    <t>player_load</t>
-  </si>
-  <si>
-    <t>top_speed_kmh</t>
-  </si>
-  <si>
-    <t>distance_per_min_mmin</t>
-  </si>
-  <si>
-    <t>power_score_wkg</t>
-  </si>
-  <si>
-    <t>work_ratio</t>
-  </si>
-  <si>
     <t>max_acceleration_mss</t>
   </si>
   <si>
@@ -483,129 +408,33 @@
     <t>dec_counts_per_min</t>
   </si>
   <si>
-    <t>Mean</t>
-  </si>
-  <si>
-    <t>Std Dev</t>
-  </si>
-  <si>
-    <t>Distance per minute</t>
-  </si>
-  <si>
     <t>Maximum Acceleration</t>
   </si>
   <si>
     <t>Maximum Deceleration</t>
   </si>
   <si>
-    <t>Accelerations per Minute</t>
-  </si>
-  <si>
-    <t>Decelerations per Minute   </t>
-  </si>
-  <si>
-    <t>    1.18</t>
-  </si>
-  <si>
-    <t>max_top_speed_kmh</t>
-  </si>
-  <si>
-    <t>max_distance_per_min_mmin</t>
-  </si>
-  <si>
-    <t>max_max_acceleration_mss</t>
-  </si>
-  <si>
-    <t>max_max_deceleration_mss</t>
-  </si>
-  <si>
-    <t>metric</t>
-  </si>
-  <si>
-    <t>player</t>
-  </si>
-  <si>
-    <t>club</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>match day</t>
-  </si>
-  <si>
-    <t>distance_km</t>
-  </si>
-  <si>
-    <t>Ronald Ssekiganda</t>
-  </si>
-  <si>
     <t>Md7</t>
   </si>
   <si>
-    <t>sprint_distance_m</t>
-  </si>
-  <si>
-    <t>Innocent Wafula Esimu</t>
-  </si>
-  <si>
     <t>Md1</t>
   </si>
   <si>
-    <t>power_plays</t>
-  </si>
-  <si>
-    <t>energy_kcal</t>
-  </si>
-  <si>
-    <t>Amos Etoju</t>
-  </si>
-  <si>
     <t>Md11</t>
   </si>
   <si>
-    <t>impacts</t>
-  </si>
-  <si>
-    <t>Blanchar Mulamba</t>
-  </si>
-  <si>
     <t>Md13</t>
   </si>
   <si>
-    <t>total_accelerations</t>
-  </si>
-  <si>
-    <t>Felix Okot</t>
-  </si>
-  <si>
     <t>Md29</t>
   </si>
   <si>
-    <t>total_decelerations</t>
-  </si>
-  <si>
-    <t>Yafeesi Mubiru</t>
-  </si>
-  <si>
-    <t>Tonny Atukunda</t>
-  </si>
-  <si>
-    <t>Andrew Kyambadde</t>
-  </si>
-  <si>
     <t>Md21</t>
   </si>
   <si>
-    <t>Aggrey Kiirya</t>
-  </si>
-  <si>
     <t>Md25</t>
   </si>
   <si>
-    <t>Frank Tumwesigye</t>
-  </si>
-  <si>
     <t>Md27</t>
   </si>
   <si>
@@ -700,16 +529,71 @@
   </si>
   <si>
     <t>Forwards</t>
+  </si>
+  <si>
+    <t>avg_top_speed_kmh</t>
+  </si>
+  <si>
+    <t>avg_distance_per_min_mmin</t>
+  </si>
+  <si>
+    <t>Average Top Speed</t>
+  </si>
+  <si>
+    <t>Average Distance</t>
+  </si>
+  <si>
+    <t>Average Distance/min</t>
+  </si>
+  <si>
+    <t>Average Sprint Distance</t>
+  </si>
+  <si>
+    <t>Average power Plays</t>
+  </si>
+  <si>
+    <t>Average Impacts</t>
+  </si>
+  <si>
+    <t>Average Player Load</t>
+  </si>
+  <si>
+    <t>Average Power Score</t>
+  </si>
+  <si>
+    <t>Average Work Ratio</t>
+  </si>
+  <si>
+    <t>Average Accs/min</t>
+  </si>
+  <si>
+    <t>Average Decs/min</t>
+  </si>
+  <si>
+    <t>Season End League Position</t>
+  </si>
+  <si>
+    <t>Kcca FC</t>
+  </si>
+  <si>
+    <t>avg_power_SCore_wkg</t>
+  </si>
+  <si>
+    <t>Average Energy</t>
+  </si>
+  <si>
+    <t>Season Average</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -764,8 +648,50 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -778,8 +704,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF333333"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9900"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -870,17 +808,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -905,10 +832,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1018,31 +946,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1058,11 +968,73 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="63">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1070,16 +1042,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1095,11 +1057,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1115,11 +1077,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1135,11 +1097,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1155,11 +1117,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1175,11 +1137,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1195,11 +1157,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1215,11 +1177,131 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1587,6 +1669,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF9900"/>
+      <color rgb="FF333333"/>
       <color rgb="FFFFFFFF"/>
       <color rgb="FF99FF33"/>
       <color rgb="FFFF0000"/>
@@ -2220,7 +2304,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$C$2</c:f>
+              <c:f>Sheet4!$E$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2330,7 +2414,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet4!$B$3:$B$18</c:f>
+              <c:f>Sheet4!$C$3:$C$18</c:f>
               <c:strCache>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
@@ -2386,7 +2470,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$C$3:$C$18</c:f>
+              <c:f>Sheet4!$E$3:$E$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -5475,13 +5559,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>180976</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
@@ -5927,17 +6011,17 @@
       <c r="L2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="N2" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="O2" s="47" t="s">
-        <v>213</v>
-      </c>
-      <c r="P2" s="47" t="s">
-        <v>214</v>
+      <c r="M2" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="N2" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="O2" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P2" s="41" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -5971,19 +6055,19 @@
       <c r="K3" s="14">
         <v>14.78</v>
       </c>
-      <c r="L3" s="46">
+      <c r="L3" s="40">
         <v>76.87</v>
       </c>
-      <c r="M3" s="48">
+      <c r="M3" s="42">
         <v>5.92</v>
       </c>
-      <c r="N3" s="48">
+      <c r="N3" s="42">
         <v>7.27</v>
       </c>
-      <c r="O3" s="48">
+      <c r="O3" s="42">
         <v>4.29</v>
       </c>
-      <c r="P3" s="48">
+      <c r="P3" s="42">
         <v>4.12</v>
       </c>
     </row>
@@ -6021,16 +6105,16 @@
       <c r="L4" s="22">
         <v>74.44</v>
       </c>
-      <c r="M4" s="48">
+      <c r="M4" s="42">
         <v>5.95</v>
       </c>
-      <c r="N4" s="48">
+      <c r="N4" s="42">
         <v>7.13</v>
       </c>
-      <c r="O4" s="48">
+      <c r="O4" s="42">
         <v>4.09</v>
       </c>
-      <c r="P4" s="48">
+      <c r="P4" s="42">
         <v>3.93</v>
       </c>
     </row>
@@ -6068,16 +6152,16 @@
       <c r="L5" s="22">
         <v>76.78</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="42">
         <v>5.89</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="42">
         <v>7.18</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="42">
         <v>4.4000000000000004</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="42">
         <v>4.2300000000000004</v>
       </c>
     </row>
@@ -6115,16 +6199,16 @@
       <c r="L6" s="22">
         <v>74.62</v>
       </c>
-      <c r="M6" s="48">
+      <c r="M6" s="42">
         <v>5.84</v>
       </c>
-      <c r="N6" s="48">
+      <c r="N6" s="42">
         <v>7.18</v>
       </c>
-      <c r="O6" s="48">
+      <c r="O6" s="42">
         <v>4.2699999999999996</v>
       </c>
-      <c r="P6" s="48">
+      <c r="P6" s="42">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -6162,16 +6246,16 @@
       <c r="L7" s="22">
         <v>77.16</v>
       </c>
-      <c r="M7" s="48">
+      <c r="M7" s="42">
         <v>5.84</v>
       </c>
-      <c r="N7" s="48">
+      <c r="N7" s="42">
         <v>7.08</v>
       </c>
-      <c r="O7" s="48">
+      <c r="O7" s="42">
         <v>4.41</v>
       </c>
-      <c r="P7" s="48">
+      <c r="P7" s="42">
         <v>4.25</v>
       </c>
     </row>
@@ -6209,16 +6293,16 @@
       <c r="L8" s="22">
         <v>71.98</v>
       </c>
-      <c r="M8" s="48">
+      <c r="M8" s="42">
         <v>5.92</v>
       </c>
-      <c r="N8" s="48">
+      <c r="N8" s="42">
         <v>7.22</v>
       </c>
-      <c r="O8" s="48">
+      <c r="O8" s="42">
         <v>3.98</v>
       </c>
-      <c r="P8" s="48">
+      <c r="P8" s="42">
         <v>3.81</v>
       </c>
     </row>
@@ -6256,16 +6340,16 @@
       <c r="L9" s="22">
         <v>72.25</v>
       </c>
-      <c r="M9" s="48">
+      <c r="M9" s="42">
         <v>5.8</v>
       </c>
-      <c r="N9" s="48">
+      <c r="N9" s="42">
         <v>7.33</v>
       </c>
-      <c r="O9" s="48">
+      <c r="O9" s="42">
         <v>3.97</v>
       </c>
-      <c r="P9" s="48">
+      <c r="P9" s="42">
         <v>3.81</v>
       </c>
     </row>
@@ -6303,16 +6387,16 @@
       <c r="L10" s="22">
         <v>72.739999999999995</v>
       </c>
-      <c r="M10" s="48">
+      <c r="M10" s="42">
         <v>5.77</v>
       </c>
-      <c r="N10" s="48">
+      <c r="N10" s="42">
         <v>7.36</v>
       </c>
-      <c r="O10" s="48">
+      <c r="O10" s="42">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P10" s="48">
+      <c r="P10" s="42">
         <v>3.94</v>
       </c>
     </row>
@@ -6350,16 +6434,16 @@
       <c r="L11" s="22">
         <v>74.28</v>
       </c>
-      <c r="M11" s="48">
+      <c r="M11" s="42">
         <v>5.75</v>
       </c>
-      <c r="N11" s="48">
+      <c r="N11" s="42">
         <v>7.16</v>
       </c>
-      <c r="O11" s="48">
+      <c r="O11" s="42">
         <v>4.22</v>
       </c>
-      <c r="P11" s="48">
+      <c r="P11" s="42">
         <v>4.03</v>
       </c>
     </row>
@@ -6397,16 +6481,16 @@
       <c r="L12" s="22">
         <v>75.239999999999995</v>
       </c>
-      <c r="M12" s="48">
+      <c r="M12" s="42">
         <v>5.88</v>
       </c>
-      <c r="N12" s="48">
+      <c r="N12" s="42">
         <v>7.24</v>
       </c>
-      <c r="O12" s="48">
+      <c r="O12" s="42">
         <v>4.28</v>
       </c>
-      <c r="P12" s="48">
+      <c r="P12" s="42">
         <v>4.12</v>
       </c>
     </row>
@@ -6444,16 +6528,16 @@
       <c r="L13" s="22">
         <v>69.34</v>
       </c>
-      <c r="M13" s="48">
+      <c r="M13" s="42">
         <v>5.81</v>
       </c>
-      <c r="N13" s="48">
+      <c r="N13" s="42">
         <v>7.19</v>
       </c>
-      <c r="O13" s="48">
+      <c r="O13" s="42">
         <v>3.88</v>
       </c>
-      <c r="P13" s="48">
+      <c r="P13" s="42">
         <v>3.72</v>
       </c>
     </row>
@@ -6491,16 +6575,16 @@
       <c r="L14" s="22">
         <v>73.63</v>
       </c>
-      <c r="M14" s="48">
+      <c r="M14" s="42">
         <v>5.9</v>
       </c>
-      <c r="N14" s="48">
+      <c r="N14" s="42">
         <v>7.22</v>
       </c>
-      <c r="O14" s="48">
+      <c r="O14" s="42">
         <v>4.05</v>
       </c>
-      <c r="P14" s="48">
+      <c r="P14" s="42">
         <v>3.87</v>
       </c>
     </row>
@@ -6538,16 +6622,16 @@
       <c r="L15" s="22">
         <v>72.62</v>
       </c>
-      <c r="M15" s="48">
+      <c r="M15" s="42">
         <v>5.87</v>
       </c>
-      <c r="N15" s="48">
+      <c r="N15" s="42">
         <v>6.95</v>
       </c>
-      <c r="O15" s="48">
+      <c r="O15" s="42">
         <v>3.97</v>
       </c>
-      <c r="P15" s="48">
+      <c r="P15" s="42">
         <v>3.8</v>
       </c>
     </row>
@@ -6585,16 +6669,16 @@
       <c r="L16" s="22">
         <v>72.47</v>
       </c>
-      <c r="M16" s="48">
+      <c r="M16" s="42">
         <v>5.86</v>
       </c>
-      <c r="N16" s="48">
+      <c r="N16" s="42">
         <v>7.09</v>
       </c>
-      <c r="O16" s="48">
+      <c r="O16" s="42">
         <v>3.99</v>
       </c>
-      <c r="P16" s="48">
+      <c r="P16" s="42">
         <v>3.83</v>
       </c>
     </row>
@@ -6632,16 +6716,16 @@
       <c r="L17" s="22">
         <v>71.040000000000006</v>
       </c>
-      <c r="M17" s="48">
+      <c r="M17" s="42">
         <v>5.87</v>
       </c>
-      <c r="N17" s="48">
+      <c r="N17" s="42">
         <v>7.01</v>
       </c>
-      <c r="O17" s="48">
+      <c r="O17" s="42">
         <v>4.01</v>
       </c>
-      <c r="P17" s="48">
+      <c r="P17" s="42">
         <v>3.86</v>
       </c>
     </row>
@@ -6679,16 +6763,16 @@
       <c r="L18" s="22">
         <v>70.58</v>
       </c>
-      <c r="M18" s="48">
+      <c r="M18" s="42">
         <v>5.79</v>
       </c>
-      <c r="N18" s="48">
+      <c r="N18" s="42">
         <v>7.24</v>
       </c>
-      <c r="O18" s="48">
+      <c r="O18" s="42">
         <v>3.82</v>
       </c>
-      <c r="P18" s="48">
+      <c r="P18" s="42">
         <v>3.66</v>
       </c>
     </row>
@@ -6726,16 +6810,16 @@
       <c r="L19" s="22">
         <v>67.260000000000005</v>
       </c>
-      <c r="M19" s="48">
+      <c r="M19" s="42">
         <v>5.98</v>
       </c>
-      <c r="N19" s="48">
+      <c r="N19" s="42">
         <v>7.25</v>
       </c>
-      <c r="O19" s="48">
+      <c r="O19" s="42">
         <v>3.76</v>
       </c>
-      <c r="P19" s="48">
+      <c r="P19" s="42">
         <v>3.62</v>
       </c>
     </row>
@@ -6773,16 +6857,16 @@
       <c r="L20" s="22">
         <v>67.260000000000005</v>
       </c>
-      <c r="M20" s="48">
+      <c r="M20" s="42">
         <v>5.85</v>
       </c>
-      <c r="N20" s="48">
+      <c r="N20" s="42">
         <v>7.09</v>
       </c>
-      <c r="O20" s="48">
+      <c r="O20" s="42">
         <v>3.76</v>
       </c>
-      <c r="P20" s="48">
+      <c r="P20" s="42">
         <v>3.62</v>
       </c>
     </row>
@@ -6820,16 +6904,16 @@
       <c r="L21" s="22">
         <v>71.66</v>
       </c>
-      <c r="M21" s="48">
+      <c r="M21" s="42">
         <v>5.84</v>
       </c>
-      <c r="N21" s="48">
+      <c r="N21" s="42">
         <v>7.19</v>
       </c>
-      <c r="O21" s="48">
+      <c r="O21" s="42">
         <v>3.99</v>
       </c>
-      <c r="P21" s="48">
+      <c r="P21" s="42">
         <v>3.82</v>
       </c>
     </row>
@@ -6867,16 +6951,16 @@
       <c r="L22" s="22">
         <v>67.989999999999995</v>
       </c>
-      <c r="M22" s="48">
+      <c r="M22" s="42">
         <v>5.84</v>
       </c>
-      <c r="N22" s="48">
+      <c r="N22" s="42">
         <v>7.13</v>
       </c>
-      <c r="O22" s="48">
+      <c r="O22" s="42">
         <v>3.73</v>
       </c>
-      <c r="P22" s="48">
+      <c r="P22" s="42">
         <v>3.59</v>
       </c>
     </row>
@@ -6914,16 +6998,16 @@
       <c r="L23" s="22">
         <v>67.150000000000006</v>
       </c>
-      <c r="M23" s="48">
+      <c r="M23" s="42">
         <v>5.87</v>
       </c>
-      <c r="N23" s="48">
+      <c r="N23" s="42">
         <v>7.23</v>
       </c>
-      <c r="O23" s="48">
+      <c r="O23" s="42">
         <v>3.82</v>
       </c>
-      <c r="P23" s="48">
+      <c r="P23" s="42">
         <v>3.66</v>
       </c>
     </row>
@@ -6961,16 +7045,16 @@
       <c r="L24" s="22">
         <v>75.81</v>
       </c>
-      <c r="M24" s="48">
+      <c r="M24" s="42">
         <v>5.93</v>
       </c>
-      <c r="N24" s="48">
+      <c r="N24" s="42">
         <v>6.95</v>
       </c>
-      <c r="O24" s="48">
+      <c r="O24" s="42">
         <v>4.1900000000000004</v>
       </c>
-      <c r="P24" s="48">
+      <c r="P24" s="42">
         <v>4.0199999999999996</v>
       </c>
     </row>
@@ -7008,16 +7092,16 @@
       <c r="L25" s="22">
         <v>69.45</v>
       </c>
-      <c r="M25" s="48">
+      <c r="M25" s="42">
         <v>5.78</v>
       </c>
-      <c r="N25" s="48">
+      <c r="N25" s="42">
         <v>7.4</v>
       </c>
-      <c r="O25" s="48">
+      <c r="O25" s="42">
         <v>3.96</v>
       </c>
-      <c r="P25" s="48">
+      <c r="P25" s="42">
         <v>3.8</v>
       </c>
     </row>
@@ -7055,16 +7139,16 @@
       <c r="L26" s="22">
         <v>71.180000000000007</v>
       </c>
-      <c r="M26" s="48">
+      <c r="M26" s="42">
         <v>5.82</v>
       </c>
-      <c r="N26" s="48">
+      <c r="N26" s="42">
         <v>7.06</v>
       </c>
-      <c r="O26" s="48">
+      <c r="O26" s="42">
         <v>3.96</v>
       </c>
-      <c r="P26" s="48">
+      <c r="P26" s="42">
         <v>3.81</v>
       </c>
     </row>
@@ -7102,16 +7186,16 @@
       <c r="L27" s="22">
         <v>74.3</v>
       </c>
-      <c r="M27" s="48">
+      <c r="M27" s="42">
         <v>5.8</v>
       </c>
-      <c r="N27" s="48">
+      <c r="N27" s="42">
         <v>7.26</v>
       </c>
-      <c r="O27" s="48">
+      <c r="O27" s="42">
         <v>4.09</v>
       </c>
-      <c r="P27" s="48">
+      <c r="P27" s="42">
         <v>3.93</v>
       </c>
     </row>
@@ -7149,16 +7233,16 @@
       <c r="L28" s="22">
         <v>73.38</v>
       </c>
-      <c r="M28" s="48">
+      <c r="M28" s="42">
         <v>5.9</v>
       </c>
-      <c r="N28" s="48">
+      <c r="N28" s="42">
         <v>7.14</v>
       </c>
-      <c r="O28" s="48">
+      <c r="O28" s="42">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P28" s="48">
+      <c r="P28" s="42">
         <v>3.94</v>
       </c>
     </row>
@@ -7196,16 +7280,16 @@
       <c r="L29" s="22">
         <v>79.06</v>
       </c>
-      <c r="M29" s="48">
+      <c r="M29" s="42">
         <v>5.74</v>
       </c>
-      <c r="N29" s="48">
+      <c r="N29" s="42">
         <v>7.2</v>
       </c>
-      <c r="O29" s="48">
+      <c r="O29" s="42">
         <v>4.33</v>
       </c>
-      <c r="P29" s="48">
+      <c r="P29" s="42">
         <v>4.16</v>
       </c>
     </row>
@@ -7243,16 +7327,16 @@
       <c r="L30" s="22">
         <v>74.73</v>
       </c>
-      <c r="M30" s="48">
+      <c r="M30" s="42">
         <v>5.81</v>
       </c>
-      <c r="N30" s="48">
+      <c r="N30" s="42">
         <v>6.89</v>
       </c>
-      <c r="O30" s="48">
+      <c r="O30" s="42">
         <v>4.1399999999999997</v>
       </c>
-      <c r="P30" s="48">
+      <c r="P30" s="42">
         <v>3.98</v>
       </c>
     </row>
@@ -7290,16 +7374,16 @@
       <c r="L31" s="22">
         <v>72.489999999999995</v>
       </c>
-      <c r="M31" s="48">
+      <c r="M31" s="42">
         <v>5.85</v>
       </c>
-      <c r="N31" s="48">
+      <c r="N31" s="42">
         <v>7.1</v>
       </c>
-      <c r="O31" s="48">
+      <c r="O31" s="42">
         <v>4.2699999999999996</v>
       </c>
-      <c r="P31" s="48">
+      <c r="P31" s="42">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -7337,16 +7421,16 @@
       <c r="L32" s="22">
         <v>70.849999999999994</v>
       </c>
-      <c r="M32" s="48">
+      <c r="M32" s="42">
         <v>5.84</v>
       </c>
-      <c r="N32" s="48">
+      <c r="N32" s="42">
         <v>7.15</v>
       </c>
-      <c r="O32" s="48">
+      <c r="O32" s="42">
         <v>3.92</v>
       </c>
-      <c r="P32" s="48">
+      <c r="P32" s="42">
         <v>3.75</v>
       </c>
     </row>
@@ -7476,48 +7560,6 @@
       <c r="I63" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J3:J32">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="aboveAverage" dxfId="51" priority="31" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="50" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K32">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="aboveAverage" dxfId="49" priority="29" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="48" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L32">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="aboveAverage" dxfId="47" priority="27" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="46" priority="28"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C3:C32">
     <cfRule type="colorScale" priority="47">
       <colorScale>
@@ -7529,10 +7571,10 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="48" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="48" operator="lessThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="49" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="49" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7547,10 +7589,10 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="51" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="51" operator="lessThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="52" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="52" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7565,10 +7607,10 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="54" operator="lessThan">
+    <cfRule type="cellIs" dxfId="58" priority="54" operator="lessThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="55" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="55" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7583,10 +7625,10 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="57" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="57" operator="lessThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="55" priority="58" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7601,10 +7643,10 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="60" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="60" operator="lessThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="61" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7619,10 +7661,10 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="63" operator="lessThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="64" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="64" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7637,12 +7679,54 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="66" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="66" operator="lessThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="67" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="67" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J32">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="aboveAverage" dxfId="48" priority="31" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="47" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K32">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="aboveAverage" dxfId="46" priority="29" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="45" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L32">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="aboveAverage" dxfId="44" priority="27" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="43" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M32">
     <cfRule type="colorScale" priority="4">
@@ -7655,8 +7739,8 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="aboveAverage" dxfId="15" priority="11" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="14" priority="12"/>
+    <cfRule type="aboveAverage" dxfId="42" priority="11" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="41" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N32">
     <cfRule type="colorScale" priority="3">
@@ -7669,8 +7753,8 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="aboveAverage" dxfId="13" priority="9" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="12" priority="10"/>
+    <cfRule type="aboveAverage" dxfId="40" priority="9" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="39" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O32">
     <cfRule type="colorScale" priority="2">
@@ -7683,8 +7767,8 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="aboveAverage" dxfId="11" priority="7" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="10" priority="8"/>
+    <cfRule type="aboveAverage" dxfId="38" priority="7" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="37" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P32">
     <cfRule type="colorScale" priority="1">
@@ -7697,8 +7781,8 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="aboveAverage" dxfId="9" priority="5" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="8" priority="6"/>
+    <cfRule type="aboveAverage" dxfId="36" priority="5" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="35" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8216,7 +8300,7 @@
       </c>
     </row>
     <row r="29" spans="2:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="B29" s="49"/>
+      <c r="B29" s="43"/>
       <c r="C29" s="21" t="s">
         <v>1</v>
       </c>
@@ -8242,30 +8326,30 @@
         <v>10</v>
       </c>
       <c r="K29" s="21" t="s">
-        <v>215</v>
+        <v>158</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>216</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
+        <v>160</v>
+      </c>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="30"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="50"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="51" t="s">
-        <v>218</v>
+      <c r="B31" s="45" t="s">
+        <v>161</v>
       </c>
       <c r="C31" s="3">
         <v>9.0500000000000007</v>
@@ -8299,8 +8383,8 @@
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B32" s="51" t="s">
-        <v>219</v>
+      <c r="B32" s="45" t="s">
+        <v>162</v>
       </c>
       <c r="C32" s="3">
         <v>8.7200000000000006</v>
@@ -8334,8 +8418,8 @@
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B33" s="51" t="s">
-        <v>220</v>
+      <c r="B33" s="45" t="s">
+        <v>163</v>
       </c>
       <c r="C33" s="3">
         <v>7.59</v>
@@ -8370,31 +8454,31 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C34">
-        <f>SUM(C31:C33)</f>
+        <f t="shared" ref="C34:I34" si="2">SUM(C31:C33)</f>
         <v>25.360000000000003</v>
       </c>
       <c r="D34">
-        <f>SUM(D31:D33)</f>
+        <f t="shared" si="2"/>
         <v>2546.1</v>
       </c>
       <c r="E34">
-        <f>SUM(E31:E33)</f>
+        <f t="shared" si="2"/>
         <v>181.24</v>
       </c>
       <c r="F34">
-        <f>SUM(F31:F33)</f>
+        <f t="shared" si="2"/>
         <v>19.12</v>
       </c>
-      <c r="G34" s="52">
-        <f>SUM(G31:G33)</f>
+      <c r="G34" s="46">
+        <f t="shared" si="2"/>
         <v>3100.17</v>
       </c>
       <c r="H34">
-        <f>SUM(H31:H33)</f>
+        <f t="shared" si="2"/>
         <v>1165.73</v>
       </c>
       <c r="I34">
-        <f>SUM(I31:I33)</f>
+        <f t="shared" si="2"/>
         <v>41.61</v>
       </c>
       <c r="K34">
@@ -8407,13 +8491,13 @@
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B36" s="51"/>
+      <c r="B36" s="45"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B37" s="51"/>
+      <c r="B37" s="45"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B38" s="51"/>
+      <c r="B38" s="45"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
@@ -8432,15 +8516,15 @@
         <v>6</v>
       </c>
       <c r="H41" t="s">
-        <v>215</v>
+        <v>158</v>
       </c>
       <c r="I41" t="s">
-        <v>216</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>218</v>
+        <v>161</v>
       </c>
       <c r="C42">
         <v>35.69</v>
@@ -8466,7 +8550,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="C43">
         <v>34.380000000000003</v>
@@ -8492,7 +8576,7 @@
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="C44">
         <v>29.93</v>
@@ -8525,1916 +8609,2547 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B25C8B-028E-49DA-9F7E-B91A315D61CC}">
-  <dimension ref="B2:N85"/>
+  <dimension ref="B2:X66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="32.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="0.140625" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" customWidth="1"/>
-    <col min="11" max="11" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="10" width="8.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" customWidth="1"/>
+    <col min="15" max="15" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+    <row r="2" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="21" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="F2" s="57"/>
+    </row>
+    <row r="3" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1">
         <v>11.21</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+      <c r="F3" s="58"/>
+    </row>
+    <row r="4" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1">
         <v>11.17</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+      <c r="F4" s="58"/>
+    </row>
+    <row r="5" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1">
         <v>10.9</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+      <c r="F5" s="58"/>
+    </row>
+    <row r="6" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1">
         <v>10.79</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
+      <c r="F6" s="58"/>
+    </row>
+    <row r="7" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="1">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1">
         <v>10.76</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+      <c r="F7" s="58"/>
+    </row>
+    <row r="8" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="1">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1">
         <v>10.72</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
+      <c r="F8" s="58"/>
+    </row>
+    <row r="9" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="1">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1">
         <v>10.44</v>
       </c>
-    </row>
-    <row r="10" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+      <c r="F9" s="58"/>
+    </row>
+    <row r="10" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="1">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1">
         <v>10.25</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+      <c r="F10" s="58"/>
+    </row>
+    <row r="11" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="1">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1">
         <v>9.89</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
+      <c r="F11" s="58"/>
+    </row>
+    <row r="12" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="1">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1">
         <v>9.6300000000000008</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
+      <c r="F12" s="58"/>
+    </row>
+    <row r="13" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="1">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1">
         <v>9.23</v>
       </c>
-    </row>
-    <row r="14" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+      <c r="F13" s="58"/>
+    </row>
+    <row r="14" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="1">
+      <c r="D14" s="1"/>
+      <c r="E14" s="1">
         <v>8.3699999999999992</v>
       </c>
-    </row>
-    <row r="15" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
+      <c r="F14" s="58"/>
+    </row>
+    <row r="15" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="1">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1">
         <v>8.09</v>
       </c>
-    </row>
-    <row r="16" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
+      <c r="F15" s="58"/>
+    </row>
+    <row r="16" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="1">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1">
         <v>7.53</v>
       </c>
-    </row>
-    <row r="17" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
+      <c r="F16" s="58"/>
+    </row>
+    <row r="17" spans="3:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="1">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
+      <c r="F17" s="58"/>
+    </row>
+    <row r="18" spans="3:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="1">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1">
         <v>6.27</v>
       </c>
-    </row>
-    <row r="23" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="2:11" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" s="38" t="s">
+      <c r="F18" s="58"/>
+    </row>
+    <row r="29" spans="3:24" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="I29" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="L29" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="M29" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="N29" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="I24" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="K24" s="41" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="C25" s="40">
+      <c r="O29" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="P29" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q29" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="R29" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="S29" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="T29" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="U29" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="V29" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="W29" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="X29" s="48" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C30" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42">
+        <v>29.481831</v>
+      </c>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42">
+        <v>87.510609000000002</v>
+      </c>
+      <c r="H30" s="42">
+        <v>8.8946900000000007</v>
+      </c>
+      <c r="I30" s="42">
+        <v>778.05620099999999</v>
+      </c>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42">
+        <v>57.985869999999998</v>
+      </c>
+      <c r="L30" s="42">
+        <v>1126.760822</v>
+      </c>
+      <c r="M30" s="42">
+        <v>5.7840670000000003</v>
+      </c>
+      <c r="N30" s="42">
+        <v>399.76299899999998</v>
+      </c>
+      <c r="O30" s="42">
+        <v>417.80338499999999</v>
+      </c>
+      <c r="P30" s="42">
+        <f>ROUND(O30,2)</f>
+        <v>417.8</v>
+      </c>
+      <c r="Q30" s="42">
+        <f>ROUND(N30,2)</f>
+        <v>399.76</v>
+      </c>
+      <c r="R30" s="42">
+        <v>403.10897899999998</v>
+      </c>
+      <c r="S30" s="42">
+        <v>14.326917</v>
+      </c>
+      <c r="T30" s="42">
+        <v>73.620771000000005</v>
+      </c>
+      <c r="U30" s="42">
+        <v>4.2101550000000003</v>
+      </c>
+      <c r="V30" s="42">
+        <v>4.0292770000000004</v>
+      </c>
+      <c r="W30" s="42">
+        <f>ROUND(U30,2)</f>
+        <v>4.21</v>
+      </c>
+      <c r="X30" s="42">
+        <f>ROUND(V30,2)</f>
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C31" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42">
+        <v>29.394945</v>
+      </c>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42">
+        <v>86.903322000000003</v>
+      </c>
+      <c r="H31" s="42">
+        <v>8.7705769999999994</v>
+      </c>
+      <c r="I31" s="42">
+        <v>884.55066099999999</v>
+      </c>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42">
+        <v>64.241230999999999</v>
+      </c>
+      <c r="L31" s="42">
+        <v>1090.3917429999999</v>
+      </c>
+      <c r="M31" s="42">
+        <v>6.6707330000000002</v>
+      </c>
+      <c r="N31" s="42">
+        <v>426.66216900000001</v>
+      </c>
+      <c r="O31" s="42">
+        <v>445.51865400000003</v>
+      </c>
+      <c r="P31" s="42">
+        <f>ROUND(O31,2)</f>
+        <v>445.52</v>
+      </c>
+      <c r="Q31" s="42">
+        <f>ROUND(N31,2)</f>
+        <v>426.66</v>
+      </c>
+      <c r="R31" s="42">
+        <v>419.48384700000003</v>
+      </c>
+      <c r="S31" s="42">
+        <v>14.411045</v>
+      </c>
+      <c r="T31" s="42">
+        <v>74.298349000000002</v>
+      </c>
+      <c r="U31" s="42">
+        <v>4.4863730000000004</v>
+      </c>
+      <c r="V31" s="42">
+        <v>4.2968169999999999</v>
+      </c>
+      <c r="W31" s="42">
+        <f>ROUND(U31,2)</f>
+        <v>4.49</v>
+      </c>
+      <c r="X31" s="42">
+        <f>ROUND(V31,2)</f>
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C32" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42">
+        <v>30.422006</v>
+      </c>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42">
+        <v>91.540171999999998</v>
+      </c>
+      <c r="H32" s="42">
+        <v>9.1178360000000005</v>
+      </c>
+      <c r="I32" s="42">
+        <v>1000.6119179999999</v>
+      </c>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42">
+        <v>69.973506</v>
+      </c>
+      <c r="L32" s="42">
+        <v>1116.8063159999999</v>
+      </c>
+      <c r="M32" s="42">
+        <v>5.7419760000000002</v>
+      </c>
+      <c r="N32" s="42">
+        <v>409.69849599999998</v>
+      </c>
+      <c r="O32" s="42">
+        <v>427.64752499999997</v>
+      </c>
+      <c r="P32" s="42">
+        <f>ROUND(O32,2)</f>
+        <v>427.65</v>
+      </c>
+      <c r="Q32" s="42">
+        <f>ROUND(N32,2)</f>
+        <v>409.7</v>
+      </c>
+      <c r="R32" s="42">
+        <v>408.45667500000002</v>
+      </c>
+      <c r="S32" s="42">
+        <v>14.955090999999999</v>
+      </c>
+      <c r="T32" s="42">
+        <v>78.625810999999999</v>
+      </c>
+      <c r="U32" s="42">
+        <v>4.3178599999999996</v>
+      </c>
+      <c r="V32" s="42">
+        <v>4.1367839999999996</v>
+      </c>
+      <c r="W32" s="42">
+        <f>ROUND(U32,2)</f>
+        <v>4.32</v>
+      </c>
+      <c r="X32" s="42">
+        <f>ROUND(V32,2)</f>
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C33" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42">
+        <v>29.718781</v>
+      </c>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42">
+        <v>83.700630000000004</v>
+      </c>
+      <c r="H33" s="42">
+        <v>8.3171680000000006</v>
+      </c>
+      <c r="I33" s="42">
+        <v>810.65083700000002</v>
+      </c>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42">
+        <v>56.721128</v>
+      </c>
+      <c r="L33" s="42">
+        <v>1010.228404</v>
+      </c>
+      <c r="M33" s="42">
+        <v>5.5084010000000001</v>
+      </c>
+      <c r="N33" s="42">
+        <v>361.61679500000002</v>
+      </c>
+      <c r="O33" s="42">
+        <v>380.23534100000001</v>
+      </c>
+      <c r="P33" s="42">
+        <f>ROUND(O33,2)</f>
+        <v>380.24</v>
+      </c>
+      <c r="Q33" s="42">
+        <f>ROUND(N33,2)</f>
+        <v>361.62</v>
+      </c>
+      <c r="R33" s="42">
+        <v>384.22066799999999</v>
+      </c>
+      <c r="S33" s="42">
+        <v>13.480930000000001</v>
+      </c>
+      <c r="T33" s="42">
+        <v>70.034812000000002</v>
+      </c>
+      <c r="U33" s="42">
+        <v>3.84111</v>
+      </c>
+      <c r="V33" s="42">
+        <v>3.6528010000000002</v>
+      </c>
+      <c r="W33" s="42">
+        <f>ROUND(U33,2)</f>
+        <v>3.84</v>
+      </c>
+      <c r="X33" s="42">
+        <f>ROUND(V33,2)</f>
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="34" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C34" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42">
+        <v>29.373066000000001</v>
+      </c>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42">
+        <v>84.232636999999997</v>
+      </c>
+      <c r="H34" s="42">
+        <v>8.3841289999999997</v>
+      </c>
+      <c r="I34" s="42">
+        <v>798.05896099999995</v>
+      </c>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42">
+        <v>58.516035000000002</v>
+      </c>
+      <c r="L34" s="42">
+        <v>1019.425761</v>
+      </c>
+      <c r="M34" s="42">
+        <v>6.4371830000000001</v>
+      </c>
+      <c r="N34" s="42">
+        <v>374.80675500000001</v>
+      </c>
+      <c r="O34" s="42">
+        <v>392.472418</v>
+      </c>
+      <c r="P34" s="42">
+        <f>ROUND(O34,2)</f>
+        <v>392.47</v>
+      </c>
+      <c r="Q34" s="42">
+        <f>ROUND(N34,2)</f>
+        <v>374.81</v>
+      </c>
+      <c r="R34" s="42">
+        <v>381.267064</v>
+      </c>
+      <c r="S34" s="42">
+        <v>13.800765999999999</v>
+      </c>
+      <c r="T34" s="42">
+        <v>72.081063</v>
+      </c>
+      <c r="U34" s="42">
+        <v>4.0128250000000003</v>
+      </c>
+      <c r="V34" s="42">
+        <v>3.8324159999999998</v>
+      </c>
+      <c r="W34" s="42">
+        <f>ROUND(U34,2)</f>
+        <v>4.01</v>
+      </c>
+      <c r="X34" s="42">
+        <f>ROUND(V34,2)</f>
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="35" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C35" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42">
+        <v>29.700538999999999</v>
+      </c>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42">
+        <v>91.864369999999994</v>
+      </c>
+      <c r="H35" s="42">
+        <v>9.0076640000000001</v>
+      </c>
+      <c r="I35" s="42">
+        <v>980.26935700000001</v>
+      </c>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42">
+        <v>68.178225999999995</v>
+      </c>
+      <c r="L35" s="42">
+        <v>1109.2271000000001</v>
+      </c>
+      <c r="M35" s="42">
+        <v>4.84971</v>
+      </c>
+      <c r="N35" s="42">
+        <v>404.93530099999998</v>
+      </c>
+      <c r="O35" s="42">
+        <v>420.60171000000003</v>
+      </c>
+      <c r="P35" s="42">
+        <f>ROUND(O35,2)</f>
+        <v>420.6</v>
+      </c>
+      <c r="Q35" s="42">
+        <f>ROUND(N35,2)</f>
+        <v>404.94</v>
+      </c>
+      <c r="R35" s="42">
+        <v>411.400553</v>
+      </c>
+      <c r="S35" s="42">
+        <v>14.962113</v>
+      </c>
+      <c r="T35" s="42">
+        <v>78.488632999999993</v>
+      </c>
+      <c r="U35" s="42">
+        <v>4.3250500000000001</v>
+      </c>
+      <c r="V35" s="42">
+        <v>4.164129</v>
+      </c>
+      <c r="W35" s="42">
+        <f>ROUND(U35,2)</f>
+        <v>4.33</v>
+      </c>
+      <c r="X35" s="42">
+        <f>ROUND(V35,2)</f>
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="36" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C36" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42">
+        <v>28.957795999999998</v>
+      </c>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42">
+        <v>84.678234000000003</v>
+      </c>
+      <c r="H36" s="42">
+        <v>8.314254</v>
+      </c>
+      <c r="I36" s="42">
+        <v>830.76728400000002</v>
+      </c>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42">
+        <v>57.936373000000003</v>
+      </c>
+      <c r="L36" s="42">
+        <v>1029.2770909999999</v>
+      </c>
+      <c r="M36" s="42">
+        <v>5.2129479999999999</v>
+      </c>
+      <c r="N36" s="42">
+        <v>356.49640900000003</v>
+      </c>
+      <c r="O36" s="42">
+        <v>368.76774899999998</v>
+      </c>
+      <c r="P36" s="42">
+        <f>ROUND(O36,2)</f>
+        <v>368.77</v>
+      </c>
+      <c r="Q36" s="42">
+        <f>ROUND(N36,2)</f>
+        <v>356.5</v>
+      </c>
+      <c r="R36" s="42">
+        <v>387.69135999999997</v>
+      </c>
+      <c r="S36" s="42">
+        <v>13.535007</v>
+      </c>
+      <c r="T36" s="42">
+        <v>70.183501000000007</v>
+      </c>
+      <c r="U36" s="42">
+        <v>3.758953</v>
+      </c>
+      <c r="V36" s="42">
+        <v>3.6340409999999999</v>
+      </c>
+      <c r="W36" s="42">
+        <f>ROUND(U36,2)</f>
+        <v>3.76</v>
+      </c>
+      <c r="X36" s="42">
+        <f>ROUND(V36,2)</f>
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="37" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C37" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42">
+        <v>29.096119000000002</v>
+      </c>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42">
+        <v>84.466273999999999</v>
+      </c>
+      <c r="H37" s="42">
+        <v>8.4018730000000001</v>
+      </c>
+      <c r="I37" s="42">
+        <v>825.58669699999996</v>
+      </c>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42">
+        <v>59.376725999999998</v>
+      </c>
+      <c r="L37" s="42">
+        <v>1019.569025</v>
+      </c>
+      <c r="M37" s="42">
+        <v>6.5753209999999997</v>
+      </c>
+      <c r="N37" s="42">
+        <v>386.23770300000001</v>
+      </c>
+      <c r="O37" s="42">
+        <v>401.50300800000002</v>
+      </c>
+      <c r="P37" s="42">
+        <f>ROUND(O37,2)</f>
+        <v>401.5</v>
+      </c>
+      <c r="Q37" s="42">
+        <f>ROUND(N37,2)</f>
+        <v>386.24</v>
+      </c>
+      <c r="R37" s="42">
+        <v>391.75424099999998</v>
+      </c>
+      <c r="S37" s="42">
+        <v>13.738329</v>
+      </c>
+      <c r="T37" s="42">
+        <v>72.952406999999994</v>
+      </c>
+      <c r="U37" s="42">
+        <v>4.0877590000000001</v>
+      </c>
+      <c r="V37" s="42">
+        <v>3.9329179999999999</v>
+      </c>
+      <c r="W37" s="42">
+        <f>ROUND(U37,2)</f>
+        <v>4.09</v>
+      </c>
+      <c r="X37" s="42">
+        <f>ROUND(V37,2)</f>
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="38" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C38" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42">
+        <v>29.436430999999999</v>
+      </c>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42">
+        <v>84.491602999999998</v>
+      </c>
+      <c r="H38" s="42">
+        <v>7.8411229999999996</v>
+      </c>
+      <c r="I38" s="42">
+        <v>760.63205500000004</v>
+      </c>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42">
+        <v>55.621091999999997</v>
+      </c>
+      <c r="L38" s="42">
+        <v>975.82920000000001</v>
+      </c>
+      <c r="M38" s="42">
+        <v>4.844017</v>
+      </c>
+      <c r="N38" s="42">
+        <v>357.98194799999999</v>
+      </c>
+      <c r="O38" s="42">
+        <v>373.78417100000001</v>
+      </c>
+      <c r="P38" s="42">
+        <f>ROUND(O38,2)</f>
+        <v>373.78</v>
+      </c>
+      <c r="Q38" s="42">
+        <f>ROUND(N38,2)</f>
+        <v>357.98</v>
+      </c>
+      <c r="R38" s="42">
+        <v>351.823825</v>
+      </c>
+      <c r="S38" s="42">
+        <v>13.720646</v>
+      </c>
+      <c r="T38" s="42">
+        <v>69.735212000000004</v>
+      </c>
+      <c r="U38" s="42">
+        <v>4.054907</v>
+      </c>
+      <c r="V38" s="42">
+        <v>3.883365</v>
+      </c>
+      <c r="W38" s="42">
+        <f>ROUND(U38,2)</f>
+        <v>4.05</v>
+      </c>
+      <c r="X38" s="42">
+        <f>ROUND(V38,2)</f>
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="39" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C39" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42">
+        <v>29.276540000000001</v>
+      </c>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42">
+        <v>86.345883000000001</v>
+      </c>
+      <c r="H39" s="42">
+        <v>8.6050269999999998</v>
+      </c>
+      <c r="I39" s="42">
+        <v>799.52132700000004</v>
+      </c>
+      <c r="J39" s="42"/>
+      <c r="K39" s="42">
+        <v>57.794077000000001</v>
+      </c>
+      <c r="L39" s="42">
+        <v>1064.720558</v>
+      </c>
+      <c r="M39" s="42">
+        <v>6.8519079999999999</v>
+      </c>
+      <c r="N39" s="42">
+        <v>391.08613800000001</v>
+      </c>
+      <c r="O39" s="42">
+        <v>406.27909899999997</v>
+      </c>
+      <c r="P39" s="42">
+        <f>ROUND(O39,2)</f>
+        <v>406.28</v>
+      </c>
+      <c r="Q39" s="42">
+        <f>ROUND(N39,2)</f>
+        <v>391.09</v>
+      </c>
+      <c r="R39" s="42">
+        <v>394.89686499999999</v>
+      </c>
+      <c r="S39" s="42">
+        <v>13.890231</v>
+      </c>
+      <c r="T39" s="42">
+        <v>70.634504000000007</v>
+      </c>
+      <c r="U39" s="42">
+        <v>4.0894009999999996</v>
+      </c>
+      <c r="V39" s="42">
+        <v>3.9369239999999999</v>
+      </c>
+      <c r="W39" s="42">
+        <f>ROUND(U39,2)</f>
+        <v>4.09</v>
+      </c>
+      <c r="X39" s="42">
+        <f>ROUND(V39,2)</f>
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="40" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C40" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42">
+        <v>30.586366000000002</v>
+      </c>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42">
+        <v>102.83889499999999</v>
+      </c>
+      <c r="H40" s="42">
         <v>10.086886</v>
       </c>
-      <c r="D25" s="40">
+      <c r="I40" s="42">
         <v>1080.2639810000001</v>
       </c>
-      <c r="E25" s="40">
+      <c r="J40" s="42"/>
+      <c r="K40" s="42">
         <v>72.126375999999993</v>
       </c>
-      <c r="F25" s="40">
+      <c r="L40" s="42">
         <v>1221.870866</v>
       </c>
-      <c r="G25" s="40">
+      <c r="M40" s="42">
         <v>7.1315869999999997</v>
       </c>
-      <c r="H25" s="40">
+      <c r="N40" s="42">
         <v>428.01444400000003</v>
       </c>
-      <c r="I25" s="40">
+      <c r="O40" s="42">
         <v>449.71499999999997</v>
       </c>
-      <c r="J25" s="40">
-        <f>ROUND(I25,2)</f>
+      <c r="P40" s="42">
+        <f>ROUND(O40,2)</f>
         <v>449.72</v>
       </c>
-      <c r="K25" s="42">
-        <f t="shared" ref="K25:K40" si="0">ROUND(H25,2)</f>
+      <c r="Q40" s="42">
+        <f>ROUND(N40,2)</f>
         <v>428.01</v>
       </c>
-    </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="40">
+      <c r="R40" s="42">
+        <v>456.488766</v>
+      </c>
+      <c r="S40" s="42">
+        <v>16.521405000000001</v>
+      </c>
+      <c r="T40" s="42">
+        <v>88.427937999999997</v>
+      </c>
+      <c r="U40" s="42">
+        <v>4.579135</v>
+      </c>
+      <c r="V40" s="42">
+        <v>4.3564189999999998</v>
+      </c>
+      <c r="W40" s="42">
+        <f>ROUND(U40,2)</f>
+        <v>4.58</v>
+      </c>
+      <c r="X40" s="42">
+        <f>ROUND(V40,2)</f>
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="3:24" ht="33" x14ac:dyDescent="0.25">
+      <c r="C41" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42">
+        <v>29.260767000000001</v>
+      </c>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42">
+        <v>98.162519000000003</v>
+      </c>
+      <c r="H41" s="42">
         <v>9.7042129999999993</v>
       </c>
-      <c r="D26" s="40">
+      <c r="I41" s="42">
         <v>862.14343899999994</v>
       </c>
-      <c r="E26" s="40">
+      <c r="J41" s="42"/>
+      <c r="K41" s="42">
         <v>64.896820000000005</v>
       </c>
-      <c r="F26" s="40">
+      <c r="L41" s="42">
         <v>1164.405773</v>
       </c>
-      <c r="G26" s="40">
+      <c r="M41" s="42">
         <v>7.8512120000000003</v>
       </c>
-      <c r="H26" s="40">
+      <c r="N41" s="42">
         <v>432.34564399999999</v>
       </c>
-      <c r="I26" s="40">
+      <c r="O41" s="42">
         <v>447.38043900000002</v>
       </c>
-      <c r="J26" s="40">
-        <f t="shared" ref="J26:J40" si="1">ROUND(I26,2)</f>
+      <c r="P41" s="42">
+        <f>ROUND(O41,2)</f>
         <v>447.38</v>
       </c>
-      <c r="K26" s="42">
-        <f t="shared" si="0"/>
+      <c r="Q41" s="42">
+        <f>ROUND(N41,2)</f>
         <v>432.35</v>
       </c>
-    </row>
-    <row r="27" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="40">
-        <v>9.1178360000000005</v>
-      </c>
-      <c r="D27" s="40">
-        <v>1000.6119179999999</v>
-      </c>
-      <c r="E27" s="40">
-        <v>69.973506</v>
-      </c>
-      <c r="F27" s="40">
-        <v>1116.8063159999999</v>
-      </c>
-      <c r="G27" s="40">
-        <v>5.7419760000000002</v>
-      </c>
-      <c r="H27" s="40">
-        <v>409.69849599999998</v>
-      </c>
-      <c r="I27" s="40">
-        <v>427.64752499999997</v>
-      </c>
-      <c r="J27" s="40">
-        <f t="shared" si="1"/>
+      <c r="R41" s="42">
+        <v>453.12781899999999</v>
+      </c>
+      <c r="S41" s="42">
+        <v>15.713335000000001</v>
+      </c>
+      <c r="T41" s="42">
+        <v>81.829293000000007</v>
+      </c>
+      <c r="U41" s="42">
+        <v>4.5508600000000001</v>
+      </c>
+      <c r="V41" s="42">
+        <v>4.398021</v>
+      </c>
+      <c r="W41" s="42">
+        <f>ROUND(U41,2)</f>
+        <v>4.55</v>
+      </c>
+      <c r="X41" s="42">
+        <f>ROUND(V41,2)</f>
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C42" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42">
+        <v>29.678196</v>
+      </c>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42">
+        <v>82.473961000000003</v>
+      </c>
+      <c r="H42" s="42">
+        <v>8.0489460000000008</v>
+      </c>
+      <c r="I42" s="42">
+        <v>807.32354499999997</v>
+      </c>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42">
+        <v>56.501353000000002</v>
+      </c>
+      <c r="L42" s="42">
+        <v>971.26029200000005</v>
+      </c>
+      <c r="M42" s="42">
+        <v>6.8365049999999998</v>
+      </c>
+      <c r="N42" s="42">
+        <v>345.08367700000002</v>
+      </c>
+      <c r="O42" s="42">
+        <v>355.82652999999999</v>
+      </c>
+      <c r="P42" s="42">
+        <f>ROUND(O42,2)</f>
+        <v>355.83</v>
+      </c>
+      <c r="Q42" s="42">
+        <f>ROUND(N42,2)</f>
+        <v>345.08</v>
+      </c>
+      <c r="R42" s="42">
+        <v>367.90340300000003</v>
+      </c>
+      <c r="S42" s="42">
+        <v>13.209262000000001</v>
+      </c>
+      <c r="T42" s="42">
+        <v>68.072078000000005</v>
+      </c>
+      <c r="U42" s="42">
+        <v>3.651284</v>
+      </c>
+      <c r="V42" s="42">
+        <v>3.5413290000000002</v>
+      </c>
+      <c r="W42" s="42">
+        <f>ROUND(U42,2)</f>
+        <v>3.65</v>
+      </c>
+      <c r="X42" s="42">
+        <f>ROUND(V42,2)</f>
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="43" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C43" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42">
+        <v>29.655118000000002</v>
+      </c>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42">
+        <v>84.423075999999995</v>
+      </c>
+      <c r="H43" s="42">
+        <v>8.5616640000000004</v>
+      </c>
+      <c r="I43" s="42">
+        <v>881.11155799999995</v>
+      </c>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42">
+        <v>61.741489999999999</v>
+      </c>
+      <c r="L43" s="42">
+        <v>1042.1979940000001</v>
+      </c>
+      <c r="M43" s="42">
+        <v>5.4715069999999999</v>
+      </c>
+      <c r="N43" s="42">
+        <v>391.74291299999999</v>
+      </c>
+      <c r="O43" s="42">
+        <v>407.70566100000002</v>
+      </c>
+      <c r="P43" s="42">
+        <f>ROUND(O43,2)</f>
+        <v>407.71</v>
+      </c>
+      <c r="Q43" s="42">
+        <f>ROUND(N43,2)</f>
+        <v>391.74</v>
+      </c>
+      <c r="R43" s="42">
+        <v>392.628714</v>
+      </c>
+      <c r="S43" s="42">
+        <v>14.016738999999999</v>
+      </c>
+      <c r="T43" s="42">
+        <v>72.532409000000001</v>
+      </c>
+      <c r="U43" s="42">
+        <v>4.148828</v>
+      </c>
+      <c r="V43" s="42">
+        <v>3.9865249999999999</v>
+      </c>
+      <c r="W43" s="42">
+        <f>ROUND(U43,2)</f>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="X43" s="42">
+        <f>ROUND(V43,2)</f>
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="44" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C44" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42">
+        <v>30.393160999999999</v>
+      </c>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42">
+        <v>87.255553000000006</v>
+      </c>
+      <c r="H44" s="42">
+        <v>8.8671769999999999</v>
+      </c>
+      <c r="I44" s="42">
+        <v>919.17026199999998</v>
+      </c>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42">
+        <v>65.189905999999993</v>
+      </c>
+      <c r="L44" s="42">
+        <v>1084.9680679999999</v>
+      </c>
+      <c r="M44" s="42">
+        <v>8.0504879999999996</v>
+      </c>
+      <c r="N44" s="42">
+        <v>396.613944</v>
+      </c>
+      <c r="O44" s="42">
+        <v>414.40724299999999</v>
+      </c>
+      <c r="P44" s="42">
+        <f>ROUND(O44,2)</f>
+        <v>414.41</v>
+      </c>
+      <c r="Q44" s="42">
+        <f>ROUND(N44,2)</f>
+        <v>396.61</v>
+      </c>
+      <c r="R44" s="42">
+        <v>409.69883199999998</v>
+      </c>
+      <c r="S44" s="42">
+        <v>14.33624</v>
+      </c>
+      <c r="T44" s="42">
+        <v>71.921205999999998</v>
+      </c>
+      <c r="U44" s="42">
+        <v>4.1315799999999996</v>
+      </c>
+      <c r="V44" s="42">
+        <v>3.9536730000000002</v>
+      </c>
+      <c r="W44" s="42">
+        <f>ROUND(U44,2)</f>
+        <v>4.13</v>
+      </c>
+      <c r="X44" s="42">
+        <f>ROUND(V44,2)</f>
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="45" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C45" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42">
+        <v>28.935934</v>
+      </c>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42">
+        <v>83.758636999999993</v>
+      </c>
+      <c r="H45" s="42">
+        <v>8.4074950000000008</v>
+      </c>
+      <c r="I45" s="42">
+        <v>811.19019800000001</v>
+      </c>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42">
+        <v>58.519765</v>
+      </c>
+      <c r="L45" s="42">
+        <v>1018.706431</v>
+      </c>
+      <c r="M45" s="42">
+        <v>7.403448</v>
+      </c>
+      <c r="N45" s="42">
+        <v>376.113744</v>
+      </c>
+      <c r="O45" s="42">
+        <v>389.91827899999998</v>
+      </c>
+      <c r="P45" s="42">
+        <f>ROUND(O45,2)</f>
+        <v>389.92</v>
+      </c>
+      <c r="Q45" s="42">
+        <f>ROUND(N45,2)</f>
+        <v>376.11</v>
+      </c>
+      <c r="R45" s="42">
+        <v>389.663411</v>
+      </c>
+      <c r="S45" s="42">
+        <v>13.554957</v>
+      </c>
+      <c r="T45" s="42">
+        <v>71.070171000000002</v>
+      </c>
+      <c r="U45" s="42">
+        <v>3.9145799999999999</v>
+      </c>
+      <c r="V45" s="42">
+        <v>3.776275</v>
+      </c>
+      <c r="W45" s="42">
+        <f>ROUND(U45,2)</f>
+        <v>3.91</v>
+      </c>
+      <c r="X45" s="42">
+        <f>ROUND(V45,2)</f>
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="46" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="47"/>
+      <c r="K46" s="47"/>
+      <c r="L46" s="47"/>
+      <c r="M46" s="47"/>
+      <c r="N46" s="47"/>
+      <c r="O46" s="47"/>
+      <c r="P46" s="47"/>
+      <c r="Q46" s="47"/>
+      <c r="R46" s="47"/>
+      <c r="S46" s="47"/>
+      <c r="T46" s="47"/>
+      <c r="U46" s="47"/>
+      <c r="V46" s="47"/>
+      <c r="W46" s="47"/>
+      <c r="X46" s="47"/>
+    </row>
+    <row r="47" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="47"/>
+      <c r="K47" s="47"/>
+      <c r="L47" s="47"/>
+      <c r="M47" s="47"/>
+      <c r="N47" s="47"/>
+      <c r="O47" s="47"/>
+      <c r="P47" s="47"/>
+      <c r="Q47" s="47"/>
+      <c r="R47" s="47"/>
+      <c r="S47" s="47"/>
+      <c r="T47" s="47"/>
+      <c r="U47" s="47"/>
+      <c r="V47" s="47"/>
+      <c r="W47" s="47"/>
+      <c r="X47" s="47"/>
+    </row>
+    <row r="48" spans="3:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="47"/>
+      <c r="K48" s="47"/>
+      <c r="L48" s="47"/>
+      <c r="M48" s="47"/>
+      <c r="N48" s="47"/>
+      <c r="O48" s="47"/>
+      <c r="P48" s="47"/>
+      <c r="Q48" s="47"/>
+      <c r="R48" s="47"/>
+      <c r="S48" s="47"/>
+      <c r="T48" s="47"/>
+      <c r="U48" s="47"/>
+      <c r="V48" s="47"/>
+      <c r="W48" s="47"/>
+      <c r="X48" s="47"/>
+    </row>
+    <row r="49" spans="2:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="E49" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="F49" s="49" t="s">
+        <v>169</v>
+      </c>
+      <c r="G49" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="H49" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="I49" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="J49" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="K49" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="L49" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="M49" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="N49" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="O49" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="P49" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q49" s="49" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B50" s="60">
+        <v>1</v>
+      </c>
+      <c r="C50" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="60">
+        <f>ROUND(H30,2)</f>
+        <v>8.89</v>
+      </c>
+      <c r="E50" s="60">
+        <f>ROUND(G30,2)</f>
+        <v>87.51</v>
+      </c>
+      <c r="F50" s="62">
+        <f>ROUND(I30,2)</f>
+        <v>778.06</v>
+      </c>
+      <c r="G50" s="60">
+        <f>ROUND(E30,2)</f>
+        <v>29.48</v>
+      </c>
+      <c r="H50" s="60">
+        <f>ROUND(K30,2)</f>
+        <v>57.99</v>
+      </c>
+      <c r="I50" s="63">
+        <f>ROUND(L30,2)</f>
+        <v>1126.76</v>
+      </c>
+      <c r="J50" s="60">
+        <f>ROUND(M30,2)</f>
+        <v>5.78</v>
+      </c>
+      <c r="K50" s="60">
+        <f>ROUND(P30,2)</f>
+        <v>417.8</v>
+      </c>
+      <c r="L50" s="60">
+        <f>ROUND(Q30,2)</f>
+        <v>399.76</v>
+      </c>
+      <c r="M50" s="60">
+        <f>ROUND(R30,2)</f>
+        <v>403.11</v>
+      </c>
+      <c r="N50" s="60">
+        <f>ROUND(S30,2)</f>
+        <v>14.33</v>
+      </c>
+      <c r="O50" s="60">
+        <f>ROUND(T30,2)</f>
+        <v>73.62</v>
+      </c>
+      <c r="P50" s="60">
+        <f>ROUND(U30,2)</f>
+        <v>4.21</v>
+      </c>
+      <c r="Q50" s="60">
+        <f>ROUND(V30,2)</f>
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B51" s="51">
+        <v>2</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" s="51">
+        <f>ROUND(H31,2)</f>
+        <v>8.77</v>
+      </c>
+      <c r="E51" s="51">
+        <f>ROUND(G31,2)</f>
+        <v>86.9</v>
+      </c>
+      <c r="F51" s="54">
+        <f>ROUND(I31,2)</f>
+        <v>884.55</v>
+      </c>
+      <c r="G51" s="51">
+        <f>ROUND(E31,2)</f>
+        <v>29.39</v>
+      </c>
+      <c r="H51" s="51">
+        <f>ROUND(K31,2)</f>
+        <v>64.239999999999995</v>
+      </c>
+      <c r="I51" s="55">
+        <f>ROUND(L31,2)</f>
+        <v>1090.3900000000001</v>
+      </c>
+      <c r="J51" s="51">
+        <f>ROUND(M31,2)</f>
+        <v>6.67</v>
+      </c>
+      <c r="K51" s="51">
+        <f>ROUND(P31,2)</f>
+        <v>445.52</v>
+      </c>
+      <c r="L51" s="51">
+        <f>ROUND(Q31,2)</f>
+        <v>426.66</v>
+      </c>
+      <c r="M51" s="51">
+        <f>ROUND(R31,2)</f>
+        <v>419.48</v>
+      </c>
+      <c r="N51" s="51">
+        <f>ROUND(S31,2)</f>
+        <v>14.41</v>
+      </c>
+      <c r="O51" s="51">
+        <f>ROUND(T31,2)</f>
+        <v>74.3</v>
+      </c>
+      <c r="P51" s="51">
+        <f>ROUND(U31,2)</f>
+        <v>4.49</v>
+      </c>
+      <c r="Q51" s="51">
+        <f>ROUND(V31,2)</f>
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B52" s="51">
+        <v>3</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" s="51">
+        <f>ROUND(H32,2)</f>
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="E52" s="51">
+        <f>ROUND(G32,2)</f>
+        <v>91.54</v>
+      </c>
+      <c r="F52" s="54">
+        <f>ROUND(I32,2)</f>
+        <v>1000.61</v>
+      </c>
+      <c r="G52" s="51">
+        <f>ROUND(E32,2)</f>
+        <v>30.42</v>
+      </c>
+      <c r="H52" s="51">
+        <f>ROUND(K32,2)</f>
+        <v>69.97</v>
+      </c>
+      <c r="I52" s="55">
+        <f>ROUND(L32,2)</f>
+        <v>1116.81</v>
+      </c>
+      <c r="J52" s="51">
+        <f>ROUND(M32,2)</f>
+        <v>5.74</v>
+      </c>
+      <c r="K52" s="51">
+        <f>ROUND(P32,2)</f>
         <v>427.65</v>
       </c>
-      <c r="K27" s="42">
-        <f t="shared" si="0"/>
+      <c r="L52" s="51">
+        <f>ROUND(Q32,2)</f>
         <v>409.7</v>
       </c>
-    </row>
-    <row r="28" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="40">
-        <v>9.0076640000000001</v>
-      </c>
-      <c r="D28" s="40">
-        <v>980.26935700000001</v>
-      </c>
-      <c r="E28" s="40">
-        <v>68.178225999999995</v>
-      </c>
-      <c r="F28" s="40">
-        <v>1109.2271000000001</v>
-      </c>
-      <c r="G28" s="40">
-        <v>4.84971</v>
-      </c>
-      <c r="H28" s="40">
-        <v>404.93530099999998</v>
-      </c>
-      <c r="I28" s="40">
-        <v>420.60171000000003</v>
-      </c>
-      <c r="J28" s="40">
-        <f t="shared" si="1"/>
+      <c r="M52" s="51">
+        <f>ROUND(R32,2)</f>
+        <v>408.46</v>
+      </c>
+      <c r="N52" s="51">
+        <f>ROUND(S32,2)</f>
+        <v>14.96</v>
+      </c>
+      <c r="O52" s="51">
+        <f>ROUND(T32,2)</f>
+        <v>78.63</v>
+      </c>
+      <c r="P52" s="51">
+        <f>ROUND(U32,2)</f>
+        <v>4.32</v>
+      </c>
+      <c r="Q52" s="51">
+        <f>ROUND(V32,2)</f>
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B53" s="51">
+        <v>4</v>
+      </c>
+      <c r="C53" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="51">
+        <f>ROUND(H33,2)</f>
+        <v>8.32</v>
+      </c>
+      <c r="E53" s="51">
+        <f>ROUND(G33,2)</f>
+        <v>83.7</v>
+      </c>
+      <c r="F53" s="54">
+        <f>ROUND(I33,2)</f>
+        <v>810.65</v>
+      </c>
+      <c r="G53" s="51">
+        <f>ROUND(E33,2)</f>
+        <v>29.72</v>
+      </c>
+      <c r="H53" s="51">
+        <f>ROUND(K33,2)</f>
+        <v>56.72</v>
+      </c>
+      <c r="I53" s="55">
+        <f>ROUND(L33,2)</f>
+        <v>1010.23</v>
+      </c>
+      <c r="J53" s="51">
+        <f>ROUND(M33,2)</f>
+        <v>5.51</v>
+      </c>
+      <c r="K53" s="51">
+        <f>ROUND(P33,2)</f>
+        <v>380.24</v>
+      </c>
+      <c r="L53" s="51">
+        <f>ROUND(Q33,2)</f>
+        <v>361.62</v>
+      </c>
+      <c r="M53" s="51">
+        <f>ROUND(R33,2)</f>
+        <v>384.22</v>
+      </c>
+      <c r="N53" s="51">
+        <f>ROUND(S33,2)</f>
+        <v>13.48</v>
+      </c>
+      <c r="O53" s="51">
+        <f>ROUND(T33,2)</f>
+        <v>70.03</v>
+      </c>
+      <c r="P53" s="51">
+        <f>ROUND(U33,2)</f>
+        <v>3.84</v>
+      </c>
+      <c r="Q53" s="51">
+        <f>ROUND(V33,2)</f>
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B54" s="51">
+        <v>5</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" s="51">
+        <f>ROUND(H34,2)</f>
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="E54" s="51">
+        <f>ROUND(G34,2)</f>
+        <v>84.23</v>
+      </c>
+      <c r="F54" s="54">
+        <f>ROUND(I34,2)</f>
+        <v>798.06</v>
+      </c>
+      <c r="G54" s="51">
+        <f>ROUND(E34,2)</f>
+        <v>29.37</v>
+      </c>
+      <c r="H54" s="51">
+        <f>ROUND(K34,2)</f>
+        <v>58.52</v>
+      </c>
+      <c r="I54" s="55">
+        <f>ROUND(L34,2)</f>
+        <v>1019.43</v>
+      </c>
+      <c r="J54" s="51">
+        <f>ROUND(M34,2)</f>
+        <v>6.44</v>
+      </c>
+      <c r="K54" s="51">
+        <f>ROUND(P34,2)</f>
+        <v>392.47</v>
+      </c>
+      <c r="L54" s="51">
+        <f>ROUND(Q34,2)</f>
+        <v>374.81</v>
+      </c>
+      <c r="M54" s="51">
+        <f>ROUND(R34,2)</f>
+        <v>381.27</v>
+      </c>
+      <c r="N54" s="51">
+        <f>ROUND(S34,2)</f>
+        <v>13.8</v>
+      </c>
+      <c r="O54" s="51">
+        <f>ROUND(T34,2)</f>
+        <v>72.08</v>
+      </c>
+      <c r="P54" s="51">
+        <f>ROUND(U34,2)</f>
+        <v>4.01</v>
+      </c>
+      <c r="Q54" s="51">
+        <f>ROUND(V34,2)</f>
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B55" s="51">
+        <v>6</v>
+      </c>
+      <c r="C55" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" s="51">
+        <f>ROUND(H35,2)</f>
+        <v>9.01</v>
+      </c>
+      <c r="E55" s="51">
+        <f>ROUND(G35,2)</f>
+        <v>91.86</v>
+      </c>
+      <c r="F55" s="54">
+        <f>ROUND(I35,2)</f>
+        <v>980.27</v>
+      </c>
+      <c r="G55" s="51">
+        <f>ROUND(E35,2)</f>
+        <v>29.7</v>
+      </c>
+      <c r="H55" s="51">
+        <f>ROUND(K35,2)</f>
+        <v>68.180000000000007</v>
+      </c>
+      <c r="I55" s="55">
+        <f>ROUND(L35,2)</f>
+        <v>1109.23</v>
+      </c>
+      <c r="J55" s="51">
+        <f>ROUND(M35,2)</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="K55" s="51">
+        <f>ROUND(P35,2)</f>
         <v>420.6</v>
       </c>
-      <c r="K28" s="42">
-        <f t="shared" si="0"/>
+      <c r="L55" s="51">
+        <f>ROUND(Q35,2)</f>
         <v>404.94</v>
       </c>
-    </row>
-    <row r="29" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="40">
-        <v>8.8946900000000007</v>
-      </c>
-      <c r="D29" s="40">
-        <v>778.05620099999999</v>
-      </c>
-      <c r="E29" s="40">
-        <v>57.985869999999998</v>
-      </c>
-      <c r="F29" s="40">
-        <v>1126.760822</v>
-      </c>
-      <c r="G29" s="40">
-        <v>5.7840670000000003</v>
-      </c>
-      <c r="H29" s="40">
-        <v>399.76299899999998</v>
-      </c>
-      <c r="I29" s="40">
-        <v>417.80338499999999</v>
-      </c>
-      <c r="J29" s="40">
-        <f t="shared" si="1"/>
-        <v>417.8</v>
-      </c>
-      <c r="K29" s="42">
-        <f t="shared" si="0"/>
-        <v>399.76</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="40">
-        <v>8.8671769999999999</v>
-      </c>
-      <c r="D30" s="40">
-        <v>919.17026199999998</v>
-      </c>
-      <c r="E30" s="40">
-        <v>65.189905999999993</v>
-      </c>
-      <c r="F30" s="40">
-        <v>1084.9680679999999</v>
-      </c>
-      <c r="G30" s="40">
-        <v>8.0504879999999996</v>
-      </c>
-      <c r="H30" s="40">
-        <v>396.613944</v>
-      </c>
-      <c r="I30" s="40">
-        <v>414.40724299999999</v>
-      </c>
-      <c r="J30" s="40">
-        <f t="shared" si="1"/>
+      <c r="M55" s="51">
+        <f>ROUND(R35,2)</f>
+        <v>411.4</v>
+      </c>
+      <c r="N55" s="51">
+        <f>ROUND(S35,2)</f>
+        <v>14.96</v>
+      </c>
+      <c r="O55" s="51">
+        <f>ROUND(T35,2)</f>
+        <v>78.489999999999995</v>
+      </c>
+      <c r="P55" s="51">
+        <f>ROUND(U35,2)</f>
+        <v>4.33</v>
+      </c>
+      <c r="Q55" s="51">
+        <f>ROUND(V35,2)</f>
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B56" s="51">
+        <v>7</v>
+      </c>
+      <c r="C56" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56" s="51">
+        <f>ROUND(H36,2)</f>
+        <v>8.31</v>
+      </c>
+      <c r="E56" s="51">
+        <f>ROUND(G36,2)</f>
+        <v>84.68</v>
+      </c>
+      <c r="F56" s="54">
+        <f>ROUND(I36,2)</f>
+        <v>830.77</v>
+      </c>
+      <c r="G56" s="51">
+        <f>ROUND(E36,2)</f>
+        <v>28.96</v>
+      </c>
+      <c r="H56" s="51">
+        <f>ROUND(K36,2)</f>
+        <v>57.94</v>
+      </c>
+      <c r="I56" s="55">
+        <f>ROUND(L36,2)</f>
+        <v>1029.28</v>
+      </c>
+      <c r="J56" s="51">
+        <f>ROUND(M36,2)</f>
+        <v>5.21</v>
+      </c>
+      <c r="K56" s="51">
+        <f>ROUND(P36,2)</f>
+        <v>368.77</v>
+      </c>
+      <c r="L56" s="51">
+        <f>ROUND(Q36,2)</f>
+        <v>356.5</v>
+      </c>
+      <c r="M56" s="51">
+        <f>ROUND(R36,2)</f>
+        <v>387.69</v>
+      </c>
+      <c r="N56" s="51">
+        <f>ROUND(S36,2)</f>
+        <v>13.54</v>
+      </c>
+      <c r="O56" s="51">
+        <f>ROUND(T36,2)</f>
+        <v>70.180000000000007</v>
+      </c>
+      <c r="P56" s="51">
+        <f>ROUND(U36,2)</f>
+        <v>3.76</v>
+      </c>
+      <c r="Q56" s="51">
+        <f>ROUND(V36,2)</f>
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B57" s="51">
+        <v>8</v>
+      </c>
+      <c r="C57" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" s="51">
+        <f>ROUND(H37,2)</f>
+        <v>8.4</v>
+      </c>
+      <c r="E57" s="51">
+        <f>ROUND(G37,2)</f>
+        <v>84.47</v>
+      </c>
+      <c r="F57" s="54">
+        <f>ROUND(I37,2)</f>
+        <v>825.59</v>
+      </c>
+      <c r="G57" s="51">
+        <f>ROUND(E37,2)</f>
+        <v>29.1</v>
+      </c>
+      <c r="H57" s="51">
+        <f>ROUND(K37,2)</f>
+        <v>59.38</v>
+      </c>
+      <c r="I57" s="55">
+        <f>ROUND(L37,2)</f>
+        <v>1019.57</v>
+      </c>
+      <c r="J57" s="51">
+        <f>ROUND(M37,2)</f>
+        <v>6.58</v>
+      </c>
+      <c r="K57" s="51">
+        <f>ROUND(P37,2)</f>
+        <v>401.5</v>
+      </c>
+      <c r="L57" s="51">
+        <f>ROUND(Q37,2)</f>
+        <v>386.24</v>
+      </c>
+      <c r="M57" s="51">
+        <f>ROUND(R37,2)</f>
+        <v>391.75</v>
+      </c>
+      <c r="N57" s="51">
+        <f>ROUND(S37,2)</f>
+        <v>13.74</v>
+      </c>
+      <c r="O57" s="51">
+        <f>ROUND(T37,2)</f>
+        <v>72.95</v>
+      </c>
+      <c r="P57" s="51">
+        <f>ROUND(U37,2)</f>
+        <v>4.09</v>
+      </c>
+      <c r="Q57" s="51">
+        <f>ROUND(V37,2)</f>
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B58" s="51">
+        <v>9</v>
+      </c>
+      <c r="C58" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58" s="51">
+        <f>ROUND(H38,2)</f>
+        <v>7.84</v>
+      </c>
+      <c r="E58" s="51">
+        <f>ROUND(G38,2)</f>
+        <v>84.49</v>
+      </c>
+      <c r="F58" s="54">
+        <f>ROUND(I38,2)</f>
+        <v>760.63</v>
+      </c>
+      <c r="G58" s="51">
+        <f>ROUND(E38,2)</f>
+        <v>29.44</v>
+      </c>
+      <c r="H58" s="51">
+        <f>ROUND(K38,2)</f>
+        <v>55.62</v>
+      </c>
+      <c r="I58" s="55">
+        <f>ROUND(L38,2)</f>
+        <v>975.83</v>
+      </c>
+      <c r="J58" s="51">
+        <f>ROUND(M38,2)</f>
+        <v>4.84</v>
+      </c>
+      <c r="K58" s="51">
+        <f>ROUND(P38,2)</f>
+        <v>373.78</v>
+      </c>
+      <c r="L58" s="51">
+        <f>ROUND(Q38,2)</f>
+        <v>357.98</v>
+      </c>
+      <c r="M58" s="51">
+        <f>ROUND(R38,2)</f>
+        <v>351.82</v>
+      </c>
+      <c r="N58" s="51">
+        <f>ROUND(S38,2)</f>
+        <v>13.72</v>
+      </c>
+      <c r="O58" s="51">
+        <f>ROUND(T38,2)</f>
+        <v>69.739999999999995</v>
+      </c>
+      <c r="P58" s="51">
+        <f>ROUND(U38,2)</f>
+        <v>4.05</v>
+      </c>
+      <c r="Q58" s="51">
+        <f>ROUND(V38,2)</f>
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B59" s="51">
+        <v>10</v>
+      </c>
+      <c r="C59" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="51">
+        <f>ROUND(H39,2)</f>
+        <v>8.61</v>
+      </c>
+      <c r="E59" s="51">
+        <f>ROUND(G39,2)</f>
+        <v>86.35</v>
+      </c>
+      <c r="F59" s="54">
+        <f>ROUND(I39,2)</f>
+        <v>799.52</v>
+      </c>
+      <c r="G59" s="51">
+        <f>ROUND(E39,2)</f>
+        <v>29.28</v>
+      </c>
+      <c r="H59" s="51">
+        <f>ROUND(K39,2)</f>
+        <v>57.79</v>
+      </c>
+      <c r="I59" s="55">
+        <f>ROUND(L39,2)</f>
+        <v>1064.72</v>
+      </c>
+      <c r="J59" s="51">
+        <f>ROUND(M39,2)</f>
+        <v>6.85</v>
+      </c>
+      <c r="K59" s="51">
+        <f>ROUND(P39,2)</f>
+        <v>406.28</v>
+      </c>
+      <c r="L59" s="51">
+        <f>ROUND(Q39,2)</f>
+        <v>391.09</v>
+      </c>
+      <c r="M59" s="51">
+        <f>ROUND(R39,2)</f>
+        <v>394.9</v>
+      </c>
+      <c r="N59" s="51">
+        <f>ROUND(S39,2)</f>
+        <v>13.89</v>
+      </c>
+      <c r="O59" s="51">
+        <f>ROUND(T39,2)</f>
+        <v>70.63</v>
+      </c>
+      <c r="P59" s="51">
+        <f>ROUND(U39,2)</f>
+        <v>4.09</v>
+      </c>
+      <c r="Q59" s="51">
+        <f>ROUND(V39,2)</f>
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B60" s="51">
+        <v>11</v>
+      </c>
+      <c r="C60" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="51">
+        <f>ROUND(H40,2)</f>
+        <v>10.09</v>
+      </c>
+      <c r="E60" s="51">
+        <f>ROUND(G40,2)</f>
+        <v>102.84</v>
+      </c>
+      <c r="F60" s="54">
+        <f>ROUND(I40,2)</f>
+        <v>1080.26</v>
+      </c>
+      <c r="G60" s="51">
+        <f>ROUND(E40,2)</f>
+        <v>30.59</v>
+      </c>
+      <c r="H60" s="51">
+        <f>ROUND(K40,2)</f>
+        <v>72.13</v>
+      </c>
+      <c r="I60" s="55">
+        <f>ROUND(L40,2)</f>
+        <v>1221.8699999999999</v>
+      </c>
+      <c r="J60" s="51">
+        <f>ROUND(M40,2)</f>
+        <v>7.13</v>
+      </c>
+      <c r="K60" s="51">
+        <f>ROUND(P40,2)</f>
+        <v>449.72</v>
+      </c>
+      <c r="L60" s="51">
+        <f>ROUND(Q40,2)</f>
+        <v>428.01</v>
+      </c>
+      <c r="M60" s="51">
+        <f>ROUND(R40,2)</f>
+        <v>456.49</v>
+      </c>
+      <c r="N60" s="51">
+        <f>ROUND(S40,2)</f>
+        <v>16.52</v>
+      </c>
+      <c r="O60" s="51">
+        <f>ROUND(T40,2)</f>
+        <v>88.43</v>
+      </c>
+      <c r="P60" s="51">
+        <f>ROUND(U40,2)</f>
+        <v>4.58</v>
+      </c>
+      <c r="Q60" s="51">
+        <f>ROUND(V40,2)</f>
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B61" s="51">
+        <v>12</v>
+      </c>
+      <c r="C61" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="51">
+        <f>ROUND(H41,2)</f>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E61" s="51">
+        <f>ROUND(G41,2)</f>
+        <v>98.16</v>
+      </c>
+      <c r="F61" s="54">
+        <f>ROUND(I41,2)</f>
+        <v>862.14</v>
+      </c>
+      <c r="G61" s="51">
+        <f>ROUND(E41,2)</f>
+        <v>29.26</v>
+      </c>
+      <c r="H61" s="51">
+        <f>ROUND(K41,2)</f>
+        <v>64.900000000000006</v>
+      </c>
+      <c r="I61" s="55">
+        <f>ROUND(L41,2)</f>
+        <v>1164.4100000000001</v>
+      </c>
+      <c r="J61" s="51">
+        <f>ROUND(M41,2)</f>
+        <v>7.85</v>
+      </c>
+      <c r="K61" s="51">
+        <f>ROUND(P41,2)</f>
+        <v>447.38</v>
+      </c>
+      <c r="L61" s="51">
+        <f>ROUND(Q41,2)</f>
+        <v>432.35</v>
+      </c>
+      <c r="M61" s="51">
+        <f>ROUND(R41,2)</f>
+        <v>453.13</v>
+      </c>
+      <c r="N61" s="51">
+        <f>ROUND(S41,2)</f>
+        <v>15.71</v>
+      </c>
+      <c r="O61" s="51">
+        <f>ROUND(T41,2)</f>
+        <v>81.83</v>
+      </c>
+      <c r="P61" s="51">
+        <f>ROUND(U41,2)</f>
+        <v>4.55</v>
+      </c>
+      <c r="Q61" s="51">
+        <f>ROUND(V41,2)</f>
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B62" s="51">
+        <v>13</v>
+      </c>
+      <c r="C62" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D62" s="51">
+        <f>ROUND(H42,2)</f>
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="E62" s="51">
+        <f>ROUND(G42,2)</f>
+        <v>82.47</v>
+      </c>
+      <c r="F62" s="54">
+        <f>ROUND(I42,2)</f>
+        <v>807.32</v>
+      </c>
+      <c r="G62" s="51">
+        <f>ROUND(E42,2)</f>
+        <v>29.68</v>
+      </c>
+      <c r="H62" s="51">
+        <f>ROUND(K42,2)</f>
+        <v>56.5</v>
+      </c>
+      <c r="I62" s="55">
+        <f>ROUND(L42,2)</f>
+        <v>971.26</v>
+      </c>
+      <c r="J62" s="51">
+        <f>ROUND(M42,2)</f>
+        <v>6.84</v>
+      </c>
+      <c r="K62" s="51">
+        <f>ROUND(P42,2)</f>
+        <v>355.83</v>
+      </c>
+      <c r="L62" s="51">
+        <f>ROUND(Q42,2)</f>
+        <v>345.08</v>
+      </c>
+      <c r="M62" s="51">
+        <f>ROUND(R42,2)</f>
+        <v>367.9</v>
+      </c>
+      <c r="N62" s="51">
+        <f>ROUND(S42,2)</f>
+        <v>13.21</v>
+      </c>
+      <c r="O62" s="51">
+        <f>ROUND(T42,2)</f>
+        <v>68.069999999999993</v>
+      </c>
+      <c r="P62" s="51">
+        <f>ROUND(U42,2)</f>
+        <v>3.65</v>
+      </c>
+      <c r="Q62" s="51">
+        <f>ROUND(V42,2)</f>
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="64">
+        <v>14</v>
+      </c>
+      <c r="C63" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" s="64">
+        <f>ROUND(H43,2)</f>
+        <v>8.56</v>
+      </c>
+      <c r="E63" s="64">
+        <f>ROUND(G43,2)</f>
+        <v>84.42</v>
+      </c>
+      <c r="F63" s="66">
+        <f>ROUND(I43,2)</f>
+        <v>881.11</v>
+      </c>
+      <c r="G63" s="64">
+        <f>ROUND(E43,2)</f>
+        <v>29.66</v>
+      </c>
+      <c r="H63" s="64">
+        <f>ROUND(K43,2)</f>
+        <v>61.74</v>
+      </c>
+      <c r="I63" s="67">
+        <f>ROUND(L43,2)</f>
+        <v>1042.2</v>
+      </c>
+      <c r="J63" s="64">
+        <f>ROUND(M43,2)</f>
+        <v>5.47</v>
+      </c>
+      <c r="K63" s="64">
+        <f>ROUND(P43,2)</f>
+        <v>407.71</v>
+      </c>
+      <c r="L63" s="64">
+        <f>ROUND(Q43,2)</f>
+        <v>391.74</v>
+      </c>
+      <c r="M63" s="64">
+        <f>ROUND(R43,2)</f>
+        <v>392.63</v>
+      </c>
+      <c r="N63" s="64">
+        <f>ROUND(S43,2)</f>
+        <v>14.02</v>
+      </c>
+      <c r="O63" s="64">
+        <f>ROUND(T43,2)</f>
+        <v>72.53</v>
+      </c>
+      <c r="P63" s="64">
+        <f>ROUND(U43,2)</f>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="Q63" s="64">
+        <f>ROUND(V43,2)</f>
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="64">
+        <v>15</v>
+      </c>
+      <c r="C64" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="D64" s="64">
+        <f>ROUND(H44,2)</f>
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="E64" s="64">
+        <f>ROUND(G44,2)</f>
+        <v>87.26</v>
+      </c>
+      <c r="F64" s="66">
+        <f>ROUND(I44,2)</f>
+        <v>919.17</v>
+      </c>
+      <c r="G64" s="64">
+        <f>ROUND(E44,2)</f>
+        <v>30.39</v>
+      </c>
+      <c r="H64" s="64">
+        <f>ROUND(K44,2)</f>
+        <v>65.19</v>
+      </c>
+      <c r="I64" s="67">
+        <f>ROUND(L44,2)</f>
+        <v>1084.97</v>
+      </c>
+      <c r="J64" s="64">
+        <f>ROUND(M44,2)</f>
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="K64" s="64">
+        <f>ROUND(P44,2)</f>
         <v>414.41</v>
       </c>
-      <c r="K30" s="42">
-        <f t="shared" si="0"/>
+      <c r="L64" s="64">
+        <f>ROUND(Q44,2)</f>
         <v>396.61</v>
       </c>
-    </row>
-    <row r="31" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="40">
-        <v>8.7705769999999994</v>
-      </c>
-      <c r="D31" s="40">
-        <v>884.55066099999999</v>
-      </c>
-      <c r="E31" s="40">
-        <v>64.241230999999999</v>
-      </c>
-      <c r="F31" s="40">
-        <v>1090.3917429999999</v>
-      </c>
-      <c r="G31" s="40">
-        <v>6.6707330000000002</v>
-      </c>
-      <c r="H31" s="40">
-        <v>426.66216900000001</v>
-      </c>
-      <c r="I31" s="40">
-        <v>445.51865400000003</v>
-      </c>
-      <c r="J31" s="40">
-        <f t="shared" si="1"/>
-        <v>445.52</v>
-      </c>
-      <c r="K31" s="42">
-        <f t="shared" si="0"/>
-        <v>426.66</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="40">
-        <v>8.6050269999999998</v>
-      </c>
-      <c r="D32" s="40">
-        <v>799.52132700000004</v>
-      </c>
-      <c r="E32" s="40">
-        <v>57.794077000000001</v>
-      </c>
-      <c r="F32" s="40">
-        <v>1064.720558</v>
-      </c>
-      <c r="G32" s="40">
-        <v>6.8519079999999999</v>
-      </c>
-      <c r="H32" s="40">
-        <v>391.08613800000001</v>
-      </c>
-      <c r="I32" s="40">
-        <v>406.27909899999997</v>
-      </c>
-      <c r="J32" s="40">
-        <f t="shared" si="1"/>
-        <v>406.28</v>
-      </c>
-      <c r="K32" s="42">
-        <f t="shared" si="0"/>
-        <v>391.09</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="40">
-        <v>8.5616640000000004</v>
-      </c>
-      <c r="D33" s="40">
-        <v>881.11155799999995</v>
-      </c>
-      <c r="E33" s="40">
-        <v>61.741489999999999</v>
-      </c>
-      <c r="F33" s="40">
-        <v>1042.1979940000001</v>
-      </c>
-      <c r="G33" s="40">
-        <v>5.4715069999999999</v>
-      </c>
-      <c r="H33" s="40">
-        <v>391.74291299999999</v>
-      </c>
-      <c r="I33" s="40">
-        <v>407.70566100000002</v>
-      </c>
-      <c r="J33" s="40">
-        <f t="shared" si="1"/>
-        <v>407.71</v>
-      </c>
-      <c r="K33" s="42">
-        <f t="shared" si="0"/>
-        <v>391.74</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" s="40">
-        <v>8.4074950000000008</v>
-      </c>
-      <c r="D34" s="40">
-        <v>811.19019800000001</v>
-      </c>
-      <c r="E34" s="40">
-        <v>58.519765</v>
-      </c>
-      <c r="F34" s="40">
-        <v>1018.706431</v>
-      </c>
-      <c r="G34" s="40">
-        <v>7.403448</v>
-      </c>
-      <c r="H34" s="40">
-        <v>376.113744</v>
-      </c>
-      <c r="I34" s="40">
-        <v>389.91827899999998</v>
-      </c>
-      <c r="J34" s="40">
-        <f t="shared" si="1"/>
+      <c r="M64" s="64">
+        <f>ROUND(R44,2)</f>
+        <v>409.7</v>
+      </c>
+      <c r="N64" s="64">
+        <f>ROUND(S44,2)</f>
+        <v>14.34</v>
+      </c>
+      <c r="O64" s="64">
+        <f>ROUND(T44,2)</f>
+        <v>71.92</v>
+      </c>
+      <c r="P64" s="64">
+        <f>ROUND(U44,2)</f>
+        <v>4.13</v>
+      </c>
+      <c r="Q64" s="64">
+        <f>ROUND(V44,2)</f>
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B65" s="64">
+        <v>16</v>
+      </c>
+      <c r="C65" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" s="64">
+        <f>ROUND(H45,2)</f>
+        <v>8.41</v>
+      </c>
+      <c r="E65" s="64">
+        <f>ROUND(G45,2)</f>
+        <v>83.76</v>
+      </c>
+      <c r="F65" s="66">
+        <f>ROUND(I45,2)</f>
+        <v>811.19</v>
+      </c>
+      <c r="G65" s="64">
+        <f>ROUND(E45,2)</f>
+        <v>28.94</v>
+      </c>
+      <c r="H65" s="64">
+        <f>ROUND(K45,2)</f>
+        <v>58.52</v>
+      </c>
+      <c r="I65" s="67">
+        <f>ROUND(L45,2)</f>
+        <v>1018.71</v>
+      </c>
+      <c r="J65" s="64">
+        <f>ROUND(M45,2)</f>
+        <v>7.4</v>
+      </c>
+      <c r="K65" s="64">
+        <f>ROUND(P45,2)</f>
         <v>389.92</v>
       </c>
-      <c r="K34" s="42">
-        <f t="shared" si="0"/>
+      <c r="L65" s="64">
+        <f>ROUND(Q45,2)</f>
         <v>376.11</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="40">
-        <v>8.4018730000000001</v>
-      </c>
-      <c r="D35" s="40">
-        <v>825.58669699999996</v>
-      </c>
-      <c r="E35" s="40">
-        <v>59.376725999999998</v>
-      </c>
-      <c r="F35" s="40">
-        <v>1019.569025</v>
-      </c>
-      <c r="G35" s="40">
-        <v>6.5753209999999997</v>
-      </c>
-      <c r="H35" s="40">
-        <v>386.23770300000001</v>
-      </c>
-      <c r="I35" s="40">
-        <v>401.50300800000002</v>
-      </c>
-      <c r="J35" s="40">
-        <f t="shared" si="1"/>
-        <v>401.5</v>
-      </c>
-      <c r="K35" s="42">
-        <f t="shared" si="0"/>
-        <v>386.24</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" s="40">
-        <v>8.3841289999999997</v>
-      </c>
-      <c r="D36" s="40">
-        <v>798.05896099999995</v>
-      </c>
-      <c r="E36" s="40">
-        <v>58.516035000000002</v>
-      </c>
-      <c r="F36" s="40">
-        <v>1019.425761</v>
-      </c>
-      <c r="G36" s="40">
-        <v>6.4371830000000001</v>
-      </c>
-      <c r="H36" s="40">
-        <v>374.80675500000001</v>
-      </c>
-      <c r="I36" s="40">
-        <v>392.472418</v>
-      </c>
-      <c r="J36" s="40">
-        <f t="shared" si="1"/>
-        <v>392.47</v>
-      </c>
-      <c r="K36" s="42">
-        <f t="shared" si="0"/>
-        <v>374.81</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="C37" s="40">
-        <v>8.3171680000000006</v>
-      </c>
-      <c r="D37" s="40">
-        <v>810.65083700000002</v>
-      </c>
-      <c r="E37" s="40">
-        <v>56.721128</v>
-      </c>
-      <c r="F37" s="40">
-        <v>1010.228404</v>
-      </c>
-      <c r="G37" s="40">
-        <v>5.5084010000000001</v>
-      </c>
-      <c r="H37" s="40">
-        <v>361.61679500000002</v>
-      </c>
-      <c r="I37" s="40">
-        <v>380.23534100000001</v>
-      </c>
-      <c r="J37" s="40">
-        <f t="shared" si="1"/>
-        <v>380.24</v>
-      </c>
-      <c r="K37" s="42">
-        <f t="shared" si="0"/>
-        <v>361.62</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C38" s="40">
-        <v>8.314254</v>
-      </c>
-      <c r="D38" s="40">
-        <v>830.76728400000002</v>
-      </c>
-      <c r="E38" s="40">
-        <v>57.936373000000003</v>
-      </c>
-      <c r="F38" s="40">
-        <v>1029.2770909999999</v>
-      </c>
-      <c r="G38" s="40">
-        <v>5.2129479999999999</v>
-      </c>
-      <c r="H38" s="40">
-        <v>356.49640900000003</v>
-      </c>
-      <c r="I38" s="40">
-        <v>368.76774899999998</v>
-      </c>
-      <c r="J38" s="40">
-        <f t="shared" si="1"/>
-        <v>368.77</v>
-      </c>
-      <c r="K38" s="42">
-        <f t="shared" si="0"/>
-        <v>356.5</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39" s="40">
-        <v>8.0489460000000008</v>
-      </c>
-      <c r="D39" s="40">
-        <v>807.32354499999997</v>
-      </c>
-      <c r="E39" s="40">
-        <v>56.501353000000002</v>
-      </c>
-      <c r="F39" s="40">
-        <v>971.26029200000005</v>
-      </c>
-      <c r="G39" s="40">
-        <v>6.8365049999999998</v>
-      </c>
-      <c r="H39" s="40">
-        <v>345.08367700000002</v>
-      </c>
-      <c r="I39" s="40">
-        <v>355.82652999999999</v>
-      </c>
-      <c r="J39" s="40">
-        <f t="shared" si="1"/>
-        <v>355.83</v>
-      </c>
-      <c r="K39" s="42">
-        <f t="shared" si="0"/>
-        <v>345.08</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="C40" s="40">
-        <v>7.8411229999999996</v>
-      </c>
-      <c r="D40" s="40">
-        <v>760.63205500000004</v>
-      </c>
-      <c r="E40" s="40">
-        <v>55.621091999999997</v>
-      </c>
-      <c r="F40" s="40">
-        <v>975.82920000000001</v>
-      </c>
-      <c r="G40" s="40">
-        <v>4.844017</v>
-      </c>
-      <c r="H40" s="40">
-        <v>357.98194799999999</v>
-      </c>
-      <c r="I40" s="40">
-        <v>373.78417100000001</v>
-      </c>
-      <c r="J40" s="40">
-        <f t="shared" si="1"/>
-        <v>373.78</v>
-      </c>
-      <c r="K40" s="42">
-        <f t="shared" si="0"/>
-        <v>357.98</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="2:11" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="D43" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E43" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="F43" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="G43" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="H43" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="I43" s="43" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="C44" s="40">
-        <v>456.488766</v>
-      </c>
-      <c r="D44" s="40">
-        <v>16.521405000000001</v>
-      </c>
-      <c r="E44" s="40">
-        <v>88.427937999999997</v>
-      </c>
-      <c r="F44" s="40">
-        <v>4.579135</v>
-      </c>
-      <c r="G44" s="40">
-        <v>4.3564189999999998</v>
-      </c>
-      <c r="H44">
-        <f>ROUND(F44,2)</f>
-        <v>4.58</v>
-      </c>
-      <c r="I44">
-        <f>ROUND(G44,2)</f>
-        <v>4.3600000000000003</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="C45" s="40">
-        <v>453.12781899999999</v>
-      </c>
-      <c r="D45" s="40">
-        <v>15.713335000000001</v>
-      </c>
-      <c r="E45" s="40">
-        <v>81.829293000000007</v>
-      </c>
-      <c r="F45" s="40">
-        <v>4.5508600000000001</v>
-      </c>
-      <c r="G45" s="40">
-        <v>4.398021</v>
-      </c>
-      <c r="H45">
-        <f t="shared" ref="H45:H59" si="2">ROUND(F45,2)</f>
-        <v>4.55</v>
-      </c>
-      <c r="I45">
-        <f t="shared" ref="I45:I59" si="3">ROUND(G45,2)</f>
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="C46" s="40">
-        <v>408.45667500000002</v>
-      </c>
-      <c r="D46" s="40">
-        <v>14.955090999999999</v>
-      </c>
-      <c r="E46" s="40">
-        <v>78.625810999999999</v>
-      </c>
-      <c r="F46" s="40">
-        <v>4.3178599999999996</v>
-      </c>
-      <c r="G46" s="40">
-        <v>4.1367839999999996</v>
-      </c>
-      <c r="H46">
-        <f t="shared" si="2"/>
-        <v>4.32</v>
-      </c>
-      <c r="I46">
-        <f t="shared" si="3"/>
-        <v>4.1399999999999997</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C47" s="40">
-        <v>411.400553</v>
-      </c>
-      <c r="D47" s="40">
-        <v>14.962113</v>
-      </c>
-      <c r="E47" s="40">
-        <v>78.488632999999993</v>
-      </c>
-      <c r="F47" s="40">
-        <v>4.3250500000000001</v>
-      </c>
-      <c r="G47" s="40">
-        <v>4.164129</v>
-      </c>
-      <c r="H47">
-        <f t="shared" si="2"/>
-        <v>4.33</v>
-      </c>
-      <c r="I47">
-        <f t="shared" si="3"/>
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" s="40">
-        <v>419.48384700000003</v>
-      </c>
-      <c r="D48" s="40">
-        <v>14.411045</v>
-      </c>
-      <c r="E48" s="40">
-        <v>74.298349000000002</v>
-      </c>
-      <c r="F48" s="40">
-        <v>4.4863730000000004</v>
-      </c>
-      <c r="G48" s="40">
-        <v>4.2968169999999999</v>
-      </c>
-      <c r="H48">
-        <f t="shared" si="2"/>
-        <v>4.49</v>
-      </c>
-      <c r="I48">
-        <f t="shared" si="3"/>
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="40">
-        <v>403.10897899999998</v>
-      </c>
-      <c r="D49" s="40">
-        <v>14.326917</v>
-      </c>
-      <c r="E49" s="40">
-        <v>73.620771000000005</v>
-      </c>
-      <c r="F49" s="40">
-        <v>4.2101550000000003</v>
-      </c>
-      <c r="G49" s="40">
-        <v>4.0292770000000004</v>
-      </c>
-      <c r="H49">
-        <f t="shared" si="2"/>
-        <v>4.21</v>
-      </c>
-      <c r="I49">
-        <f t="shared" si="3"/>
-        <v>4.03</v>
-      </c>
-      <c r="K49" s="38"/>
-      <c r="L49" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="M49" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="N49" s="38" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="50" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="C50" s="40">
-        <v>391.75424099999998</v>
-      </c>
-      <c r="D50" s="40">
-        <v>13.738329</v>
-      </c>
-      <c r="E50" s="40">
-        <v>72.952406999999994</v>
-      </c>
-      <c r="F50" s="40">
-        <v>4.0877590000000001</v>
-      </c>
-      <c r="G50" s="40">
-        <v>3.9329179999999999</v>
-      </c>
-      <c r="H50">
-        <f t="shared" si="2"/>
-        <v>4.09</v>
-      </c>
-      <c r="I50">
-        <f t="shared" si="3"/>
-        <v>3.93</v>
-      </c>
-      <c r="K50" s="39"/>
-      <c r="L50" s="40"/>
-      <c r="M50" s="40"/>
-      <c r="N50" s="40"/>
-    </row>
-    <row r="51" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" s="40">
-        <v>392.628714</v>
-      </c>
-      <c r="D51" s="40">
-        <v>14.016738999999999</v>
-      </c>
-      <c r="E51" s="40">
-        <v>72.532409000000001</v>
-      </c>
-      <c r="F51" s="40">
-        <v>4.148828</v>
-      </c>
-      <c r="G51" s="40">
-        <v>3.9865249999999999</v>
-      </c>
-      <c r="H51">
-        <f t="shared" si="2"/>
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="I51">
-        <f t="shared" si="3"/>
-        <v>3.99</v>
-      </c>
-      <c r="K51" s="39"/>
-      <c r="L51" s="40"/>
-      <c r="M51" s="40"/>
-      <c r="N51" s="40"/>
-    </row>
-    <row r="52" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" s="40">
-        <v>381.267064</v>
-      </c>
-      <c r="D52" s="40">
-        <v>13.800765999999999</v>
-      </c>
-      <c r="E52" s="40">
-        <v>72.081063</v>
-      </c>
-      <c r="F52" s="40">
-        <v>4.0128250000000003</v>
-      </c>
-      <c r="G52" s="40">
-        <v>3.8324159999999998</v>
-      </c>
-      <c r="H52">
-        <f t="shared" si="2"/>
-        <v>4.01</v>
-      </c>
-      <c r="I52">
-        <f t="shared" si="3"/>
-        <v>3.83</v>
-      </c>
-      <c r="K52" s="39"/>
-      <c r="L52" s="40"/>
-      <c r="M52" s="40"/>
-      <c r="N52" s="40"/>
-    </row>
-    <row r="53" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" s="40">
-        <v>409.69883199999998</v>
-      </c>
-      <c r="D53" s="40">
-        <v>14.33624</v>
-      </c>
-      <c r="E53" s="40">
-        <v>71.921205999999998</v>
-      </c>
-      <c r="F53" s="40">
-        <v>4.1315799999999996</v>
-      </c>
-      <c r="G53" s="40">
-        <v>3.9536730000000002</v>
-      </c>
-      <c r="H53">
-        <f t="shared" si="2"/>
-        <v>4.13</v>
-      </c>
-      <c r="I53">
-        <f t="shared" si="3"/>
-        <v>3.95</v>
-      </c>
-      <c r="K53" s="39"/>
-      <c r="L53" s="40"/>
-      <c r="M53" s="40"/>
-      <c r="N53" s="40"/>
-    </row>
-    <row r="54" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="40">
-        <v>389.663411</v>
-      </c>
-      <c r="D54" s="40">
-        <v>13.554957</v>
-      </c>
-      <c r="E54" s="40">
-        <v>71.070171000000002</v>
-      </c>
-      <c r="F54" s="40">
-        <v>3.9145799999999999</v>
-      </c>
-      <c r="G54" s="40">
-        <v>3.776275</v>
-      </c>
-      <c r="H54">
-        <f t="shared" si="2"/>
+      <c r="M65" s="64">
+        <f>ROUND(R45,2)</f>
+        <v>389.66</v>
+      </c>
+      <c r="N65" s="64">
+        <f>ROUND(S45,2)</f>
+        <v>13.55</v>
+      </c>
+      <c r="O65" s="64">
+        <f>ROUND(T45,2)</f>
+        <v>71.069999999999993</v>
+      </c>
+      <c r="P65" s="64">
+        <f>ROUND(U45,2)</f>
         <v>3.91</v>
       </c>
-      <c r="I54">
-        <f t="shared" si="3"/>
+      <c r="Q65" s="64">
+        <f>ROUND(V45,2)</f>
         <v>3.78</v>
       </c>
-      <c r="K54" s="39"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
-      <c r="N54" s="40"/>
-    </row>
-    <row r="55" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C55" s="40">
-        <v>394.89686499999999</v>
-      </c>
-      <c r="D55" s="40">
-        <v>13.890231</v>
-      </c>
-      <c r="E55" s="40">
-        <v>70.634504000000007</v>
-      </c>
-      <c r="F55" s="40">
-        <v>4.0894009999999996</v>
-      </c>
-      <c r="G55" s="40">
-        <v>3.9369239999999999</v>
-      </c>
-      <c r="H55">
-        <f t="shared" si="2"/>
-        <v>4.09</v>
-      </c>
-      <c r="I55">
-        <f t="shared" si="3"/>
-        <v>3.94</v>
-      </c>
-      <c r="K55" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="L55" s="40">
-        <v>10</v>
-      </c>
-      <c r="M55" s="40">
-        <v>5.8526220000000002</v>
-      </c>
-      <c r="N55" s="40">
-        <v>0.63400299999999998</v>
-      </c>
-    </row>
-    <row r="56" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C56" s="40">
-        <v>387.69135999999997</v>
-      </c>
-      <c r="D56" s="40">
-        <v>13.535007</v>
-      </c>
-      <c r="E56" s="40">
-        <v>70.183501000000007</v>
-      </c>
-      <c r="F56" s="40">
-        <v>3.758953</v>
-      </c>
-      <c r="G56" s="40">
-        <v>3.6340409999999999</v>
-      </c>
-      <c r="H56">
-        <f t="shared" si="2"/>
-        <v>3.76</v>
-      </c>
-      <c r="I56">
-        <f t="shared" si="3"/>
-        <v>3.63</v>
-      </c>
-      <c r="K56" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="L56" s="40">
-        <v>10</v>
-      </c>
-      <c r="M56" s="40">
-        <v>7.1660940000000002</v>
-      </c>
-      <c r="N56" s="40">
-        <v>0.97441999999999995</v>
-      </c>
-    </row>
-    <row r="57" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="C57" s="40">
-        <v>384.22066799999999</v>
-      </c>
-      <c r="D57" s="40">
-        <v>13.480930000000001</v>
-      </c>
-      <c r="E57" s="40">
-        <v>70.034812000000002</v>
-      </c>
-      <c r="F57" s="40">
-        <v>3.84111</v>
-      </c>
-      <c r="G57" s="40">
-        <v>3.6528010000000002</v>
-      </c>
-      <c r="H57">
-        <f t="shared" si="2"/>
-        <v>3.84</v>
-      </c>
-      <c r="I57">
-        <f t="shared" si="3"/>
-        <v>3.65</v>
-      </c>
-      <c r="K57" s="39"/>
-      <c r="L57" s="40"/>
-      <c r="M57" s="40"/>
-      <c r="N57" s="40"/>
-    </row>
-    <row r="58" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="C58" s="40">
-        <v>351.823825</v>
-      </c>
-      <c r="D58" s="40">
-        <v>13.720646</v>
-      </c>
-      <c r="E58" s="40">
-        <v>69.735212000000004</v>
-      </c>
-      <c r="F58" s="40">
-        <v>4.054907</v>
-      </c>
-      <c r="G58" s="40">
-        <v>3.883365</v>
-      </c>
-      <c r="H58">
-        <f t="shared" si="2"/>
-        <v>4.05</v>
-      </c>
-      <c r="I58">
-        <f t="shared" si="3"/>
-        <v>3.88</v>
-      </c>
-      <c r="K58" s="39"/>
-      <c r="L58" s="40"/>
-      <c r="M58" s="40"/>
-      <c r="N58" s="40"/>
-    </row>
-    <row r="59" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="C59" s="40">
-        <v>367.90340300000003</v>
-      </c>
-      <c r="D59" s="40">
-        <v>13.209262000000001</v>
-      </c>
-      <c r="E59" s="40">
-        <v>68.072078000000005</v>
-      </c>
-      <c r="F59" s="40">
-        <v>3.651284</v>
-      </c>
-      <c r="G59" s="40">
-        <v>3.5413290000000002</v>
-      </c>
-      <c r="H59">
-        <f t="shared" si="2"/>
-        <v>3.65</v>
-      </c>
-      <c r="I59">
-        <f t="shared" si="3"/>
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="K60" s="29"/>
-      <c r="L60" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="M60" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="N60" s="29" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="K61" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="L61" s="3">
-        <v>36.42</v>
-      </c>
-      <c r="M61" s="3">
+    </row>
+    <row r="66" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="C66" s="50"/>
+      <c r="D66" s="52">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="E66" s="52">
+        <v>87.02</v>
+      </c>
+      <c r="F66" s="59">
+        <v>847.46</v>
+      </c>
+      <c r="G66" s="52">
         <v>29.58</v>
       </c>
-      <c r="N61" s="3">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="K62" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="L62" s="3">
-        <v>136.52000000000001</v>
-      </c>
-      <c r="M62" s="3">
-        <v>87.02</v>
-      </c>
-      <c r="N62" s="3">
-        <v>24.65</v>
-      </c>
-    </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="K63" s="44" t="s">
-        <v>151</v>
-      </c>
-      <c r="L63" s="3">
-        <v>16.14</v>
-      </c>
-      <c r="M63" s="3">
-        <v>10.33</v>
-      </c>
-      <c r="N63" s="3">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="K64" s="44" t="s">
-        <v>152</v>
-      </c>
-      <c r="L64" s="3">
-        <v>20</v>
-      </c>
-      <c r="M64" s="3">
-        <v>12.39</v>
-      </c>
-      <c r="N64" s="3">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="65" spans="2:14" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="K65" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="L65" s="3">
-        <v>7.11</v>
-      </c>
-      <c r="M65" s="3">
+      <c r="H66" s="52">
+        <v>60.51</v>
+      </c>
+      <c r="I66" s="56">
+        <v>1044.08</v>
+      </c>
+      <c r="J66" s="52">
+        <v>6.29</v>
+      </c>
+      <c r="K66" s="52">
+        <v>398.47</v>
+      </c>
+      <c r="L66" s="52">
+        <v>382.57</v>
+      </c>
+      <c r="M66" s="52">
+        <v>392.41</v>
+      </c>
+      <c r="N66" s="52">
+        <v>14</v>
+      </c>
+      <c r="O66" s="52">
+        <v>72.64</v>
+      </c>
+      <c r="P66" s="52">
         <v>4.0599999999999996</v>
       </c>
-      <c r="N65" s="3">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="66" spans="2:14" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="K66" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="L66" s="3">
-        <v>6.71</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="52">
         <v>3.9</v>
       </c>
-      <c r="N66" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="67" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="2:14" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="C68" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="D68" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="E68" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="F68" s="38" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="69" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="C69" s="40">
-        <v>36.4163</v>
-      </c>
-      <c r="D69" s="40">
-        <v>123.209469</v>
-      </c>
-      <c r="E69" s="40">
-        <v>7.7111999999999998</v>
-      </c>
-      <c r="F69" s="40">
-        <v>10</v>
-      </c>
-      <c r="I69" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="J69" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="K69" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="L69" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="M69" s="38" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="70" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C70" s="40">
-        <v>36.224299999999999</v>
-      </c>
-      <c r="D70" s="40">
-        <v>128.651725</v>
-      </c>
-      <c r="E70" s="40">
-        <v>10</v>
-      </c>
-      <c r="F70" s="40">
-        <v>10</v>
-      </c>
-      <c r="I70" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="J70" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="K70" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="L70" s="40">
-        <v>13.499000000000001</v>
-      </c>
-      <c r="M70" s="40" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="71" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="C71" s="40">
-        <v>36.208300000000001</v>
-      </c>
-      <c r="D71" s="40">
-        <v>126.420948</v>
-      </c>
-      <c r="E71" s="40">
-        <v>9.7245000000000008</v>
-      </c>
-      <c r="F71" s="40">
-        <v>10</v>
-      </c>
-      <c r="I71" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="J71" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="K71" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="L71" s="40">
-        <v>2894.4430000000002</v>
-      </c>
-      <c r="M71" s="40" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="72" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="C72" s="40">
-        <v>36.016300000000001</v>
-      </c>
-      <c r="D72" s="40">
-        <v>127.241957</v>
-      </c>
-      <c r="E72" s="40">
-        <v>9.8141999999999996</v>
-      </c>
-      <c r="F72" s="40">
-        <v>10</v>
-      </c>
-      <c r="I72" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="J72" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="K72" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="L72" s="40">
-        <v>145</v>
-      </c>
-      <c r="M72" s="40" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" s="40">
-        <v>36.016300000000001</v>
-      </c>
-      <c r="D73" s="40">
-        <v>136.524292</v>
-      </c>
-      <c r="E73" s="40">
-        <v>7.4964000000000004</v>
-      </c>
-      <c r="F73" s="40">
-        <v>10</v>
-      </c>
-      <c r="I73" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="J73" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="K73" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="L73" s="40">
-        <v>1771.0479</v>
-      </c>
-      <c r="M73" s="40" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="74" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C74" s="40">
-        <v>35.840299999999999</v>
-      </c>
-      <c r="D74" s="40">
-        <v>121.878974</v>
-      </c>
-      <c r="E74" s="40">
-        <v>7.9371</v>
-      </c>
-      <c r="F74" s="40">
-        <v>10</v>
-      </c>
-      <c r="I74" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="J74" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="K74" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="L74" s="40">
-        <v>46</v>
-      </c>
-      <c r="M74" s="40" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="75" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="C75" s="40">
-        <v>35.728299999999997</v>
-      </c>
-      <c r="D75" s="40">
-        <v>124.94776899999999</v>
-      </c>
-      <c r="E75" s="40">
-        <v>10</v>
-      </c>
-      <c r="F75" s="40">
-        <v>10</v>
-      </c>
-      <c r="I75" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="J75" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="K75" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="L75" s="40">
-        <v>705</v>
-      </c>
-      <c r="M75" s="40" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="76" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="C76" s="40">
-        <v>35.568300000000001</v>
-      </c>
-      <c r="D76" s="40">
-        <v>126.309864</v>
-      </c>
-      <c r="E76" s="40">
-        <v>8.4647000000000006</v>
-      </c>
-      <c r="F76" s="40">
-        <v>10</v>
-      </c>
-      <c r="I76" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="J76" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="K76" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="L76" s="40">
-        <v>656</v>
-      </c>
-      <c r="M76" s="40" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="77" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="C77" s="40">
-        <v>35.296300000000002</v>
-      </c>
-      <c r="D77" s="40">
-        <v>124.06533</v>
-      </c>
-      <c r="E77" s="40">
-        <v>9.0934000000000008</v>
-      </c>
-      <c r="F77" s="40">
-        <v>9.8089999999999993</v>
-      </c>
-      <c r="I77" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="J77" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="K77" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="L77" s="40">
-        <v>655.9606</v>
-      </c>
-      <c r="M77" s="40" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="78" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C78" s="40">
-        <v>35.136299999999999</v>
-      </c>
-      <c r="D78" s="40">
-        <v>128.55248599999999</v>
-      </c>
-      <c r="E78" s="40">
-        <v>7.7956000000000003</v>
-      </c>
-      <c r="F78" s="40">
-        <v>10</v>
-      </c>
-      <c r="I78" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="J78" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="K78" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="L78" s="40">
-        <v>36.4163</v>
-      </c>
-      <c r="M78" s="40" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="79" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C79" s="40">
-        <v>34.768300000000004</v>
-      </c>
-      <c r="D79" s="40">
-        <v>122.893805</v>
-      </c>
-      <c r="E79" s="40">
-        <v>10</v>
-      </c>
-      <c r="F79" s="40">
-        <v>10</v>
-      </c>
-      <c r="I79" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="J79" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="K79" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="L79" s="40">
-        <v>136.524292</v>
-      </c>
-      <c r="M79" s="40" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="80" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="C80" s="40">
-        <v>34.568300000000001</v>
-      </c>
-      <c r="D80" s="40">
-        <v>127.68189</v>
-      </c>
-      <c r="E80" s="40">
-        <v>7.9112</v>
-      </c>
-      <c r="F80" s="40">
-        <v>10</v>
-      </c>
-      <c r="I80" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="J80" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="K80" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="L80" s="40">
-        <v>21.988900000000001</v>
-      </c>
-      <c r="M80" s="40" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="81" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="C81" s="40">
-        <v>34.024299999999997</v>
-      </c>
-      <c r="D81" s="40">
-        <v>123.941688</v>
-      </c>
-      <c r="E81" s="40">
-        <v>10</v>
-      </c>
-      <c r="F81" s="40">
-        <v>10</v>
-      </c>
-      <c r="I81" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="J81" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="K81" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="L81" s="40">
-        <v>122.16549999999999</v>
-      </c>
-      <c r="M81" s="40" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="82" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C82" s="40">
-        <v>33.680300000000003</v>
-      </c>
-      <c r="D82" s="40">
-        <v>126.524818</v>
-      </c>
-      <c r="E82" s="40">
-        <v>8.9092000000000002</v>
-      </c>
-      <c r="F82" s="40">
-        <v>10</v>
-      </c>
-      <c r="I82" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="J82" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="K82" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="L82" s="40">
-        <v>10</v>
-      </c>
-      <c r="M82" s="40" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="83" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C83" s="40">
-        <v>33.488300000000002</v>
-      </c>
-      <c r="D83" s="40">
-        <v>125.55492599999999</v>
-      </c>
-      <c r="E83" s="40">
-        <v>7.0800999999999998</v>
-      </c>
-      <c r="F83" s="40">
-        <v>10</v>
-      </c>
-      <c r="I83" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="J83" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="K83" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="L83" s="40">
-        <v>10</v>
-      </c>
-      <c r="M83" s="40" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="84" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C84" s="40">
-        <v>33.024299999999997</v>
-      </c>
-      <c r="D84" s="40">
-        <v>125.48669599999999</v>
-      </c>
-      <c r="E84" s="40">
-        <v>10</v>
-      </c>
-      <c r="F84" s="40">
-        <v>10</v>
-      </c>
-      <c r="I84" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="J84" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="K84" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="L84" s="40">
-        <v>7.1104390000000004</v>
-      </c>
-      <c r="M84" s="40" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="85" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I85" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="J85" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="K85" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="L85" s="40">
-        <v>6.7076289999999998</v>
-      </c>
-      <c r="M85" s="40" t="s">
-        <v>189</v>
-      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B50:Q65">
+    <sortCondition ref="B50:B65"/>
+  </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="B66:C66"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D50:D65">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="greaterThan">
+      <formula>9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E50:E65">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="greaterThan">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F50:F65">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H50:H65">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="greaterThan">
+      <formula>60</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I50:I65">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+      <formula>1500</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M50:M65">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
+      <formula>400</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G50:G65" formula="1"/>
+  </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -10841,19 +11556,19 @@
         <v>11</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="H30" s="38" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="I30" s="38" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -10863,512 +11578,512 @@
       <c r="B31" s="3">
         <v>12</v>
       </c>
-      <c r="F31" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="G31" s="40">
+      <c r="F31" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" s="39">
         <v>5.92</v>
       </c>
-      <c r="H31" s="40">
+      <c r="H31" s="39">
         <v>7.27</v>
       </c>
-      <c r="I31" s="40">
+      <c r="I31" s="39">
         <v>4.29</v>
       </c>
-      <c r="J31" s="40">
+      <c r="J31" s="39">
         <v>4.12</v>
       </c>
     </row>
     <row r="32" spans="1:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F32" s="40" t="s">
-        <v>191</v>
-      </c>
-      <c r="G32" s="40">
+      <c r="F32" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="G32" s="39">
         <v>5.95</v>
       </c>
-      <c r="H32" s="40">
+      <c r="H32" s="39">
         <v>7.13</v>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="39">
         <v>4.09</v>
       </c>
-      <c r="J32" s="40">
+      <c r="J32" s="39">
         <v>3.93</v>
       </c>
     </row>
     <row r="33" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F33" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="G33" s="40">
+      <c r="F33" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="39">
         <v>5.89</v>
       </c>
-      <c r="H33" s="40">
+      <c r="H33" s="39">
         <v>7.18</v>
       </c>
-      <c r="I33" s="40">
+      <c r="I33" s="39">
         <v>4.4000000000000004</v>
       </c>
-      <c r="J33" s="40">
+      <c r="J33" s="39">
         <v>4.2300000000000004</v>
       </c>
     </row>
     <row r="34" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F34" s="40" t="s">
-        <v>193</v>
-      </c>
-      <c r="G34" s="40">
+      <c r="F34" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="G34" s="39">
         <v>5.84</v>
       </c>
-      <c r="H34" s="40">
+      <c r="H34" s="39">
         <v>7.18</v>
       </c>
-      <c r="I34" s="40">
+      <c r="I34" s="39">
         <v>4.2699999999999996</v>
       </c>
-      <c r="J34" s="40">
+      <c r="J34" s="39">
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="35" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F35" s="40" t="s">
-        <v>194</v>
-      </c>
-      <c r="G35" s="40">
+      <c r="F35" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="G35" s="39">
         <v>5.84</v>
       </c>
-      <c r="H35" s="40">
+      <c r="H35" s="39">
         <v>7.08</v>
       </c>
-      <c r="I35" s="40">
+      <c r="I35" s="39">
         <v>4.41</v>
       </c>
-      <c r="J35" s="40">
+      <c r="J35" s="39">
         <v>4.25</v>
       </c>
     </row>
     <row r="36" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F36" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="G36" s="40">
+      <c r="F36" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="G36" s="39">
         <v>5.92</v>
       </c>
-      <c r="H36" s="40">
+      <c r="H36" s="39">
         <v>7.22</v>
       </c>
-      <c r="I36" s="40">
+      <c r="I36" s="39">
         <v>3.98</v>
       </c>
-      <c r="J36" s="40">
+      <c r="J36" s="39">
         <v>3.81</v>
       </c>
     </row>
     <row r="37" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F37" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="G37" s="40">
+      <c r="F37" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="G37" s="39">
         <v>5.8</v>
       </c>
-      <c r="H37" s="40">
+      <c r="H37" s="39">
         <v>7.33</v>
       </c>
-      <c r="I37" s="40">
+      <c r="I37" s="39">
         <v>3.97</v>
       </c>
-      <c r="J37" s="40">
+      <c r="J37" s="39">
         <v>3.81</v>
       </c>
     </row>
     <row r="38" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F38" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="G38" s="40">
+      <c r="F38" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="G38" s="39">
         <v>5.77</v>
       </c>
-      <c r="H38" s="40">
+      <c r="H38" s="39">
         <v>7.36</v>
       </c>
-      <c r="I38" s="40">
+      <c r="I38" s="39">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J38" s="40">
+      <c r="J38" s="39">
         <v>3.94</v>
       </c>
     </row>
     <row r="39" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F39" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="G39" s="40">
+      <c r="F39" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" s="39">
         <v>5.75</v>
       </c>
-      <c r="H39" s="40">
+      <c r="H39" s="39">
         <v>7.16</v>
       </c>
-      <c r="I39" s="40">
+      <c r="I39" s="39">
         <v>4.22</v>
       </c>
-      <c r="J39" s="40">
+      <c r="J39" s="39">
         <v>4.03</v>
       </c>
     </row>
     <row r="40" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F40" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="G40" s="40">
+      <c r="F40" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="39">
         <v>5.88</v>
       </c>
-      <c r="H40" s="40">
+      <c r="H40" s="39">
         <v>7.24</v>
       </c>
-      <c r="I40" s="40">
+      <c r="I40" s="39">
         <v>4.28</v>
       </c>
-      <c r="J40" s="40">
+      <c r="J40" s="39">
         <v>4.12</v>
       </c>
     </row>
     <row r="41" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F41" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="G41" s="40">
+      <c r="F41" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="G41" s="39">
         <v>5.81</v>
       </c>
-      <c r="H41" s="40">
+      <c r="H41" s="39">
         <v>7.19</v>
       </c>
-      <c r="I41" s="40">
+      <c r="I41" s="39">
         <v>3.88</v>
       </c>
-      <c r="J41" s="40">
+      <c r="J41" s="39">
         <v>3.72</v>
       </c>
     </row>
     <row r="42" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F42" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="G42" s="40">
+      <c r="F42" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="G42" s="39">
         <v>5.9</v>
       </c>
-      <c r="H42" s="40">
+      <c r="H42" s="39">
         <v>7.22</v>
       </c>
-      <c r="I42" s="40">
+      <c r="I42" s="39">
         <v>4.05</v>
       </c>
-      <c r="J42" s="40">
+      <c r="J42" s="39">
         <v>3.87</v>
       </c>
     </row>
     <row r="43" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F43" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="G43" s="40">
+      <c r="F43" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="G43" s="39">
         <v>5.87</v>
       </c>
-      <c r="H43" s="40">
+      <c r="H43" s="39">
         <v>6.95</v>
       </c>
-      <c r="I43" s="40">
+      <c r="I43" s="39">
         <v>3.97</v>
       </c>
-      <c r="J43" s="40">
+      <c r="J43" s="39">
         <v>3.8</v>
       </c>
     </row>
     <row r="44" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F44" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="G44" s="40">
+      <c r="F44" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="G44" s="39">
         <v>5.86</v>
       </c>
-      <c r="H44" s="40">
+      <c r="H44" s="39">
         <v>7.09</v>
       </c>
-      <c r="I44" s="40">
+      <c r="I44" s="39">
         <v>3.99</v>
       </c>
-      <c r="J44" s="40">
+      <c r="J44" s="39">
         <v>3.83</v>
       </c>
     </row>
     <row r="45" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F45" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="G45" s="40">
+      <c r="F45" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="G45" s="39">
         <v>5.87</v>
       </c>
-      <c r="H45" s="40">
+      <c r="H45" s="39">
         <v>7.01</v>
       </c>
-      <c r="I45" s="40">
+      <c r="I45" s="39">
         <v>4.01</v>
       </c>
-      <c r="J45" s="40">
+      <c r="J45" s="39">
         <v>3.86</v>
       </c>
     </row>
     <row r="46" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F46" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="G46" s="40">
+      <c r="F46" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" s="39">
         <v>5.79</v>
       </c>
-      <c r="H46" s="40">
+      <c r="H46" s="39">
         <v>7.24</v>
       </c>
-      <c r="I46" s="40">
+      <c r="I46" s="39">
         <v>3.82</v>
       </c>
-      <c r="J46" s="40">
+      <c r="J46" s="39">
         <v>3.66</v>
       </c>
     </row>
     <row r="47" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F47" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="G47" s="40">
+      <c r="F47" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="G47" s="39">
         <v>5.98</v>
       </c>
-      <c r="H47" s="40">
+      <c r="H47" s="39">
         <v>7.25</v>
       </c>
-      <c r="I47" s="40">
+      <c r="I47" s="39">
         <v>3.76</v>
       </c>
-      <c r="J47" s="40">
+      <c r="J47" s="39">
         <v>3.62</v>
       </c>
     </row>
     <row r="48" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F48" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="G48" s="40">
+      <c r="F48" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="G48" s="39">
         <v>5.85</v>
       </c>
-      <c r="H48" s="40">
+      <c r="H48" s="39">
         <v>7.09</v>
       </c>
-      <c r="I48" s="40">
+      <c r="I48" s="39">
         <v>3.76</v>
       </c>
-      <c r="J48" s="40">
+      <c r="J48" s="39">
         <v>3.62</v>
       </c>
     </row>
     <row r="49" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F49" s="40" t="s">
-        <v>205</v>
-      </c>
-      <c r="G49" s="40">
+      <c r="F49" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="G49" s="39">
         <v>5.84</v>
       </c>
-      <c r="H49" s="40">
+      <c r="H49" s="39">
         <v>7.19</v>
       </c>
-      <c r="I49" s="40">
+      <c r="I49" s="39">
         <v>3.99</v>
       </c>
-      <c r="J49" s="40">
+      <c r="J49" s="39">
         <v>3.82</v>
       </c>
     </row>
     <row r="50" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F50" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="G50" s="40">
+      <c r="F50" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="G50" s="39">
         <v>5.84</v>
       </c>
-      <c r="H50" s="40">
+      <c r="H50" s="39">
         <v>7.13</v>
       </c>
-      <c r="I50" s="40">
+      <c r="I50" s="39">
         <v>3.73</v>
       </c>
-      <c r="J50" s="40">
+      <c r="J50" s="39">
         <v>3.59</v>
       </c>
     </row>
     <row r="51" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F51" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="G51" s="40">
+      <c r="F51" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="G51" s="39">
         <v>5.87</v>
       </c>
-      <c r="H51" s="40">
+      <c r="H51" s="39">
         <v>7.23</v>
       </c>
-      <c r="I51" s="40">
+      <c r="I51" s="39">
         <v>3.82</v>
       </c>
-      <c r="J51" s="40">
+      <c r="J51" s="39">
         <v>3.66</v>
       </c>
     </row>
     <row r="52" spans="6:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F52" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="G52" s="40">
+      <c r="F52" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" s="39">
         <v>5.93</v>
       </c>
-      <c r="H52" s="40">
+      <c r="H52" s="39">
         <v>6.95</v>
       </c>
-      <c r="I52" s="40">
+      <c r="I52" s="39">
         <v>4.1900000000000004</v>
       </c>
-      <c r="J52" s="40">
+      <c r="J52" s="39">
         <v>4.0199999999999996</v>
       </c>
     </row>
     <row r="53" spans="6:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F53" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="G53" s="40">
+      <c r="F53" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="G53" s="39">
         <v>5.78</v>
       </c>
-      <c r="H53" s="40">
+      <c r="H53" s="39">
         <v>7.4</v>
       </c>
-      <c r="I53" s="40">
+      <c r="I53" s="39">
         <v>3.96</v>
       </c>
-      <c r="J53" s="40">
+      <c r="J53" s="39">
         <v>3.8</v>
       </c>
     </row>
     <row r="54" spans="6:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F54" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="G54" s="40">
+      <c r="F54" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="G54" s="39">
         <v>5.82</v>
       </c>
-      <c r="H54" s="40">
+      <c r="H54" s="39">
         <v>7.06</v>
       </c>
-      <c r="I54" s="40">
+      <c r="I54" s="39">
         <v>3.96</v>
       </c>
-      <c r="J54" s="40">
+      <c r="J54" s="39">
         <v>3.81</v>
       </c>
     </row>
     <row r="55" spans="6:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F55" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="G55" s="40">
+      <c r="F55" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="G55" s="39">
         <v>5.8</v>
       </c>
-      <c r="H55" s="40">
+      <c r="H55" s="39">
         <v>7.26</v>
       </c>
-      <c r="I55" s="40">
+      <c r="I55" s="39">
         <v>4.09</v>
       </c>
-      <c r="J55" s="40">
+      <c r="J55" s="39">
         <v>3.93</v>
       </c>
     </row>
     <row r="56" spans="6:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F56" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="G56" s="40">
+      <c r="F56" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="G56" s="39">
         <v>5.9</v>
       </c>
-      <c r="H56" s="40">
+      <c r="H56" s="39">
         <v>7.14</v>
       </c>
-      <c r="I56" s="40">
+      <c r="I56" s="39">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J56" s="40">
+      <c r="J56" s="39">
         <v>3.94</v>
       </c>
     </row>
     <row r="57" spans="6:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F57" s="40" t="s">
-        <v>189</v>
-      </c>
-      <c r="G57" s="40">
+      <c r="F57" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="G57" s="39">
         <v>5.74</v>
       </c>
-      <c r="H57" s="40">
+      <c r="H57" s="39">
         <v>7.2</v>
       </c>
-      <c r="I57" s="40">
+      <c r="I57" s="39">
         <v>4.33</v>
       </c>
-      <c r="J57" s="40">
+      <c r="J57" s="39">
         <v>4.16</v>
       </c>
     </row>
     <row r="58" spans="6:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F58" s="40" t="s">
-        <v>211</v>
-      </c>
-      <c r="G58" s="40">
+      <c r="F58" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="G58" s="39">
         <v>5.81</v>
       </c>
-      <c r="H58" s="40">
+      <c r="H58" s="39">
         <v>6.89</v>
       </c>
-      <c r="I58" s="40">
+      <c r="I58" s="39">
         <v>4.1399999999999997</v>
       </c>
-      <c r="J58" s="40">
+      <c r="J58" s="39">
         <v>3.98</v>
       </c>
     </row>
     <row r="59" spans="6:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F59" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="G59" s="40">
+      <c r="F59" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="G59" s="39">
         <v>5.85</v>
       </c>
-      <c r="H59" s="40">
+      <c r="H59" s="39">
         <v>7.1</v>
       </c>
-      <c r="I59" s="40">
+      <c r="I59" s="39">
         <v>4.2699999999999996</v>
       </c>
-      <c r="J59" s="40">
+      <c r="J59" s="39">
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="60" spans="6:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F60" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="G60" s="40">
+      <c r="F60" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="G60" s="39">
         <v>5.84</v>
       </c>
-      <c r="H60" s="40">
+      <c r="H60" s="39">
         <v>7.15</v>
       </c>
-      <c r="I60" s="40">
+      <c r="I60" s="39">
         <v>3.92</v>
       </c>
-      <c r="J60" s="40">
+      <c r="J60" s="39">
         <v>3.75</v>
       </c>
     </row>
@@ -11384,8 +12099,8 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="aboveAverage" dxfId="7" priority="11" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="6" priority="12"/>
+    <cfRule type="aboveAverage" dxfId="34" priority="11" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="33" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31:H60">
     <cfRule type="colorScale" priority="3">
@@ -11398,8 +12113,8 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="aboveAverage" dxfId="5" priority="9" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="4" priority="10"/>
+    <cfRule type="aboveAverage" dxfId="32" priority="9" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="31" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31:I60">
     <cfRule type="colorScale" priority="2">
@@ -11412,8 +12127,8 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="aboveAverage" dxfId="3" priority="7" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="2" priority="8"/>
+    <cfRule type="aboveAverage" dxfId="30" priority="7" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="29" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:J60">
     <cfRule type="colorScale" priority="1">
@@ -11426,8 +12141,8 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="aboveAverage" dxfId="1" priority="5" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="0" priority="6"/>
+    <cfRule type="aboveAverage" dxfId="28" priority="5" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="27" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
